--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/NPSMedalliaequaltricsculligan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/NPS Franquias/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214C79D5-981C-4934-94FA-774887436A38}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9F7506C-0E86-4557-BACF-E1FFEFB99F88}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1369</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1414</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11075" uniqueCount="1548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11314" uniqueCount="1586">
   <si>
     <t>ID</t>
   </si>
@@ -4467,9 +4467,6 @@
     <t>Não atribuído</t>
   </si>
   <si>
-    <t>P1</t>
-  </si>
-  <si>
     <t>PF</t>
   </si>
   <si>
@@ -4814,6 +4811,147 @@
   </si>
   <si>
     <t>Nos últimos meses, a qualidade do serviço prestado tem deixado muito a desejar. Em diversas ocasiões, as visitas técnicas foram agendadas e não ocorreram. Quando acontecem ,muitas vezes são marcadas para dias em que o escritório está fechado,( mesmo o agendamento tendo sido feito para o dia em que está aberto, não respeitando a data )sem flexibilidade ou boa vontade por parte do técnico para buscar uma alternativa. A mudança na qualidade do atendimento foi bastante significativa, infelizmente para pior. Esperamos uma melhora nesse cenário ,pois caso essa situação persista , provavelmente teremos que buscar outro fornecedor. Sem contar que solicitei alteração tanto para e-mail como para número de telefone e não ocorreu.</t>
+  </si>
+  <si>
+    <t>Na primeira visita nao foi feito o serviço, os atendentes foram muito educados porém nao souberam e nao tinham as peças necessárias para resolver. No dia seguinte veio outra pessoa, ela trouxe a peça mas o problema não resolveu. Como não fui eu pessoalmente quem acompanhou não detectei no momento e tive que abrir outro chamado. Apesar de eu relatar que gostaria de um encaixe rápido pois havia passado por duas visitas que nao resolveram tive que esperar 1 semana para próxima, que ainda vai ocorrer.</t>
+  </si>
+  <si>
+    <t>O filtro foi trocado e ficou um barulho enorme no purificador, tentei pedir o reparo e só tem vaga para 01/08. Um absurdo!</t>
+  </si>
+  <si>
+    <t>PORQUE NAO TEM RESPOSABILIDADE EM FAZER AS MANUTEÇOES NA DATA CERTAS, PRECISA ESTA LIGANDO PRA LEMBRA QUE ESTA VENCIDA .</t>
+  </si>
+  <si>
+    <t>Vocês já marcaram a manutenção 3 vezes e nao apareceram. Pessimo serviço. Quero saber o procedimento para cancelamento do contrato.</t>
+  </si>
+  <si>
+    <t>Olá,
+Sugiro uma melhoria nos aspectos de organização, planejamento e comunicação, principalmente no envio de avisos com antecedência ao cliente sobre as visitas técnicas.
+Também é importante aprimorar o processo relacionado às Ordens de Serviço, informando de forma clara qual equipamento será atendido durante a manutenção.
+Esses pontos ainda não estão sendo atendidos de maneira satisfatória, o que impacta a qualidade do atendimento. Por esse motivo, no momento, seria pouco provável que eu recomendasse esse serviço a um amigo ou colega.
+Atenciosamente,
+Ieda Castelo -(Triospuma Ind. e Com. Ltda)</t>
+  </si>
+  <si>
+    <t>Carteira comunicação</t>
+  </si>
+  <si>
+    <t>Mais uma vez o técnico não foi no dia agendado</t>
+  </si>
+  <si>
+    <t>Compareceu sem agendamento e ouve uma instalação que o purificador esta solto e desnivelado</t>
+  </si>
+  <si>
+    <t>serviços não foi finalizado, segundo técnico retomaria no dia seguinte, até o momento não tivemos retorno, canal digital de comunicação e ruim.</t>
+  </si>
+  <si>
+    <t>Install</t>
+  </si>
+  <si>
+    <t>FRQ BAIXADA SERRANA RJ R01</t>
+  </si>
+  <si>
+    <t>Pedi instalação na parede e não veio , além de desmarcar a instalação e nem avisar</t>
+  </si>
+  <si>
+    <t>Não recebi o serviço de manutenção</t>
+  </si>
+  <si>
+    <t>Há cerca de 3 meses, estou com dificuldades para conseguir pagar, tanto débito automático quanto boleto, e também para agendamento de visitas e correção de defeito no equipamento. Há quase 2 meses sem funcionar
+Assistência está deixando muito a desejar</t>
+  </si>
+  <si>
+    <t>Problemas no faturamento</t>
+  </si>
+  <si>
+    <t>O bebedouro passou a apresentar vazamento no mês de ABRIL/26,solicitei prontamente o reparo, fui orientado a paralisar o uso. Só que a visita do técnico para reparo só ocorreu em JULHO.
+Ressalto que os débitos em conta pelo uso do bebedouro ocorreram de abril a junho.</t>
+  </si>
+  <si>
+    <t>Meu filtro continuou estragado na água gelada, o filtro trocado ficou</t>
+  </si>
+  <si>
+    <t>FRQ GUARULHOS SP R03</t>
+  </si>
+  <si>
+    <t>Atendimento péssimo, e o problema não foi solucionado.
+O mesmo informou que o equipamento não é para uso empresarial então não comporta a saída de água com gás</t>
+  </si>
+  <si>
+    <t>Tenho 8 protocolos, debito duplicado, 20 dias esperando estorno, péssimo atendimento jo whatsap, pedido de demonstrativo financeiro negado  apesar de 2 protocolos, pedido dd verificação de débito duplicado em julho sem resposta. estou acionando o Procon, não vou pagar mensalidade de julho enquanto nao estorarem o valor. e se ninguem resolver vou proceder com o cancelamento e assinar com o concorrente</t>
+  </si>
+  <si>
+    <t>A pressão da água no meu apartamento é altíssima. O técnico da Brastemp que instalou o equipamento há pouco mais de 6 meses instalou um redutor de pressão, que funcionava muito bem. O técnico que esteve agora, ao que parece, retirou o redutor. Está muito difícil usar o filtro porque a água sai com muita força, molhando tudo em volta!!</t>
+  </si>
+  <si>
+    <t>Demora nos retornos dos emails</t>
+  </si>
+  <si>
+    <t>FRQ RIBEIRAO PRETO R04</t>
+  </si>
+  <si>
+    <t>A central de atendimento ao cliente é horrível, abem chamados errados ocasionando custos desnecessários para vocês mesmos e não resolvem o problema do cliente, os pobres dos técnicos são maravilhosos, mas as informações que chegam até eles são completamente erradas, ligo na central por um motivo o técnico chega em minha residência por motivo completamente errados e sem ter como resolver o verdadeiro problema, já estou a um mês sem conseguir utilizar meu equipamento e pagando normalmente o aluguel, e já estou no aguardo do quarto chamado pra tentar resolver, 
+completamente insatisfeito</t>
+  </si>
+  <si>
+    <t>Só tende um robo
+O técnico não comparece e nem avisa
+o robô não consegue enviar a senha para identificar o prestador
+Mandar e-mails com ofertas não solicitadas é crime</t>
+  </si>
+  <si>
+    <t>Demorou 4 meses para trocarem um equipamento antigo, que estava superaquecendo, inclusive com laudo de técnico da Brastemp pedindo a substituição.
+Desde abril.26 com problema, só deram atenção depois que paguei as mensalidades de abril a julho.26, e solicitei o cancelamento.
+Ao ligar para cancelar, logo atenderam a necessidade, trocando o equipamento.
+Sou cliente a mais de uma década, e sempre busquei o valor do serviço, não o preço, mas hoje, o valor só serviço da Brastemp é muito baixo, para o preço que cobram.
+Como proporam trocar o equipamento e não cobrar os próximos meses, para compensar o que tive que pagar, aceitar para avaliar os seus serviços, que está deixando a desejar.
+Muito insatisfeito com o tratamento da Brastemp.</t>
+  </si>
+  <si>
+    <t>É sério? Pedi a troca do purificador que estava com defeito e trocaram por outro que não funciona. A água não gela. Estou há três dias tentando falar com vcs e nada / uma vergonha. Vou cancelar</t>
+  </si>
+  <si>
+    <t>Porque fiz contato oara marcar a manutenção, que ocorreu somente 15 dias depois, o tecnico nao resolveu o probelma no dia, voltou depois de 7 dias, nao resolveu o problema, e agora disse que voltara 10 dias depois para trocar o Filtro. Serviço no qual eu ja havia sinalizado e falaram que deveria ter a avaliação do tecnico.
+Ou seja, estou pagando por um serviço de locação mensal e faz 1 mes que estou sem filtro!</t>
+  </si>
+  <si>
+    <t>Desorganização e desrespeito com o consuidor - 1) Sempre paguei a Brastemp corretamente e em debito automático. E me gerou impactos ao trocar de cnpj x meu débito automático e eu, que nunca devi na vida, fiquei com pendência e até hj não consigo mais colocar em débito automático novamente.
+2) Marcaram de vir no Sábado, das 8 às 13h. Desmarquei todos os meus compromissos para recebê-los e além de não virem, nem sequer informaram para que eu pudesse então, resolver outras responsabilidades. 
+3) Reagendei para uma 5af à tarde e me apareceu um técnico aqui antes do dia marcado. Eu estava operada. E depois apareceu um outro técnico no dia marcado, foi quando descobrimos que a ordem de serviço anterior não tinha sido fechada. Ou seja, gerou ineficiência até para o técnico do dia marcado, pois poderia atender outros clientes. .</t>
+  </si>
+  <si>
+    <t>FRQ LAGOS RJ R02</t>
+  </si>
+  <si>
+    <t>Péssimo serviço. Desmarcaram sem avisar. Vieram num dia diferente do agendado. E não trocaram o filtro. Na época da Brastemp sempre trocaram. Triste.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A comunicação com a Culligan é horrivel, mando diversos email para o financeiro por exemplo e não temos retorno algum nem por email , nem por nenhum outro meio de comunicação. Em alguns casos temos problemas urgente com os bebedouros e já chegaram a marcar visita com mais de uma mês, e até ? todos ficam sem água? 
+Tenho mais de 50 bebedouros, já pedi a base atualizada, até hoje sem retorno. 
+Difícil demais qualquer tipo de comunicação ou retorno. </t>
+  </si>
+  <si>
+    <t>o serviço ta cada vez pior. Estou bastante descontente. estou com problemas em algumas peças que ha 8 meses espero para troca e nada. estou pensando seriamente em cancelar, pois não esta mais valendo a pena</t>
+  </si>
+  <si>
+    <t>FRQ SALVADOR BA R01 - MATRIZ</t>
+  </si>
+  <si>
+    <t>Na última agenda marcada, o técnico não compareceu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nao foi resolvido o problema preciso nova visita  urgente </t>
+  </si>
+  <si>
+    <t>FRQ GALEAO SUL RJ R05</t>
+  </si>
+  <si>
+    <t>Estou sem filtro a mais de 45 dias, estou pagamento minhas faturas e estou gastando comprando água.
+Isso é uma falta de respeito com o cliente, sou clientes a mais de 12 anos e tenho que passar por isso.
+Chega ser lamentável essa situação.</t>
+  </si>
+  <si>
+    <t>O técnico foi fazer a manutenção semestral e deixou o filtro com um barulho ensurdecedor.</t>
   </si>
 </sst>
 </file>
@@ -4870,7 +5008,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4883,6 +5021,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5186,7 +5327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1384"/>
+  <dimension ref="A1:K1414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -5515,7 +5656,7 @@
         <v>1404</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -5550,7 +5691,7 @@
         <v>1404</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -5620,7 +5761,7 @@
         <v>1404</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -5655,7 +5796,7 @@
         <v>1404</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -5970,7 +6111,7 @@
         <v>1404</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -6005,7 +6146,7 @@
         <v>1404</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -6075,7 +6216,7 @@
         <v>1404</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -6390,7 +6531,7 @@
         <v>1404</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -6460,7 +6601,7 @@
         <v>1404</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -6565,7 +6706,7 @@
         <v>1404</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -6600,7 +6741,7 @@
         <v>1404</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -6670,7 +6811,7 @@
         <v>1404</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -7020,7 +7161,7 @@
         <v>1404</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -7055,7 +7196,7 @@
         <v>1404</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -7230,7 +7371,7 @@
         <v>1404</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -7300,7 +7441,7 @@
         <v>1404</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -7650,7 +7791,7 @@
         <v>1404</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -7720,7 +7861,7 @@
         <v>1404</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -7860,7 +8001,7 @@
         <v>1404</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -7965,7 +8106,7 @@
         <v>1404</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -8070,7 +8211,7 @@
         <v>1404</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -8105,7 +8246,7 @@
         <v>1404</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -8140,7 +8281,7 @@
         <v>1404</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -8280,7 +8421,7 @@
         <v>1404</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -8560,7 +8701,7 @@
         <v>1404</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -8630,7 +8771,7 @@
         <v>1404</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -8700,7 +8841,7 @@
         <v>1404</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -8840,7 +8981,7 @@
         <v>1404</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -9050,7 +9191,7 @@
         <v>1404</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -9365,7 +9506,7 @@
         <v>1404</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -9400,7 +9541,7 @@
         <v>1404</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -9505,7 +9646,7 @@
         <v>1404</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -9750,7 +9891,7 @@
         <v>1404</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -9855,7 +9996,7 @@
         <v>1404</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -10660,7 +10801,7 @@
         <v>1404</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -10800,7 +10941,7 @@
         <v>1404</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -11080,7 +11221,7 @@
         <v>1404</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -11220,7 +11361,7 @@
         <v>1404</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -11325,7 +11466,7 @@
         <v>1404</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -11360,7 +11501,7 @@
         <v>1404</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -11745,7 +11886,7 @@
         <v>1404</v>
       </c>
       <c r="K187" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -12025,7 +12166,7 @@
         <v>1404</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -12130,7 +12271,7 @@
         <v>1404</v>
       </c>
       <c r="K198" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -12305,7 +12446,7 @@
         <v>1404</v>
       </c>
       <c r="K203" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -12515,7 +12656,7 @@
         <v>1404</v>
       </c>
       <c r="K209" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -12550,7 +12691,7 @@
         <v>1404</v>
       </c>
       <c r="K210" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -12655,7 +12796,7 @@
         <v>1404</v>
       </c>
       <c r="K213" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -12760,7 +12901,7 @@
         <v>1404</v>
       </c>
       <c r="K216" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -12900,7 +13041,7 @@
         <v>1404</v>
       </c>
       <c r="K220" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -13075,7 +13216,7 @@
         <v>1404</v>
       </c>
       <c r="K225" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -13635,7 +13776,7 @@
         <v>1404</v>
       </c>
       <c r="K241" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -13670,7 +13811,7 @@
         <v>1404</v>
       </c>
       <c r="K242" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -13705,7 +13846,7 @@
         <v>1404</v>
       </c>
       <c r="K243" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -13740,7 +13881,7 @@
         <v>1404</v>
       </c>
       <c r="K244" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -14055,7 +14196,7 @@
         <v>1404</v>
       </c>
       <c r="K253" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -14265,7 +14406,7 @@
         <v>1404</v>
       </c>
       <c r="K259" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -14335,7 +14476,7 @@
         <v>1404</v>
       </c>
       <c r="K261" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -14685,7 +14826,7 @@
         <v>1404</v>
       </c>
       <c r="K271" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -15420,7 +15561,7 @@
         <v>1404</v>
       </c>
       <c r="K292" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -15490,7 +15631,7 @@
         <v>1404</v>
       </c>
       <c r="K294" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -15525,7 +15666,7 @@
         <v>1404</v>
       </c>
       <c r="K295" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -15630,7 +15771,7 @@
         <v>1404</v>
       </c>
       <c r="K298" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -16295,7 +16436,7 @@
         <v>1404</v>
       </c>
       <c r="K317" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
@@ -16365,7 +16506,7 @@
         <v>1404</v>
       </c>
       <c r="K319" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
@@ -16820,7 +16961,7 @@
         <v>1404</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
@@ -16855,7 +16996,7 @@
         <v>1404</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
@@ -16890,7 +17031,7 @@
         <v>1404</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
@@ -16960,7 +17101,7 @@
         <v>1404</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
@@ -17205,7 +17346,7 @@
         <v>1404</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
@@ -17240,7 +17381,7 @@
         <v>1404</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
@@ -17345,7 +17486,7 @@
         <v>1404</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -17485,7 +17626,7 @@
         <v>1404</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
@@ -17555,7 +17696,7 @@
         <v>1404</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
@@ -17695,7 +17836,7 @@
         <v>1404</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
@@ -17870,7 +18011,7 @@
         <v>1404</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
@@ -17905,7 +18046,7 @@
         <v>1404</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
@@ -17975,7 +18116,7 @@
         <v>1404</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
@@ -18395,7 +18536,7 @@
         <v>1404</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
@@ -18955,7 +19096,7 @@
         <v>1404</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
@@ -19095,7 +19236,7 @@
         <v>1404</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
@@ -19445,7 +19586,7 @@
         <v>1404</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
@@ -19655,7 +19796,7 @@
         <v>1404</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
@@ -19830,7 +19971,7 @@
         <v>1404</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.25">
@@ -19865,7 +20006,7 @@
         <v>1404</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
@@ -19900,7 +20041,7 @@
         <v>1404</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
@@ -19970,7 +20111,7 @@
         <v>1404</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.25">
@@ -20180,7 +20321,7 @@
         <v>1404</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
@@ -20320,7 +20461,7 @@
         <v>1404</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
@@ -20355,7 +20496,7 @@
         <v>1404</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
@@ -20390,7 +20531,7 @@
         <v>1404</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.25">
@@ -21125,7 +21266,7 @@
         <v>1404</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
@@ -21160,7 +21301,7 @@
         <v>1404</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
@@ -21230,7 +21371,7 @@
         <v>1404</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
@@ -21300,7 +21441,7 @@
         <v>1404</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
@@ -21370,7 +21511,7 @@
         <v>1404</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
@@ -21825,7 +21966,7 @@
         <v>1404</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.25">
@@ -21965,7 +22106,7 @@
         <v>1404</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.25">
@@ -22000,7 +22141,7 @@
         <v>1404</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.25">
@@ -22490,7 +22631,7 @@
         <v>1404</v>
       </c>
       <c r="K494" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.25">
@@ -22525,7 +22666,7 @@
         <v>1404</v>
       </c>
       <c r="K495" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.25">
@@ -22735,7 +22876,7 @@
         <v>1404</v>
       </c>
       <c r="K501" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.25">
@@ -22770,7 +22911,7 @@
         <v>1404</v>
       </c>
       <c r="K502" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.25">
@@ -22805,7 +22946,7 @@
         <v>1404</v>
       </c>
       <c r="K503" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.25">
@@ -22945,7 +23086,7 @@
         <v>1404</v>
       </c>
       <c r="K507" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.25">
@@ -23505,7 +23646,7 @@
         <v>1404</v>
       </c>
       <c r="K523" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.25">
@@ -23610,7 +23751,7 @@
         <v>1404</v>
       </c>
       <c r="K526" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.25">
@@ -24100,7 +24241,7 @@
         <v>1404</v>
       </c>
       <c r="K540" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.25">
@@ -24240,7 +24381,7 @@
         <v>1404</v>
       </c>
       <c r="K544" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.25">
@@ -24310,7 +24451,7 @@
         <v>1404</v>
       </c>
       <c r="K546" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.25">
@@ -24450,7 +24591,7 @@
         <v>1404</v>
       </c>
       <c r="K550" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
@@ -24835,7 +24976,7 @@
         <v>1404</v>
       </c>
       <c r="K561" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.25">
@@ -25220,7 +25361,7 @@
         <v>1404</v>
       </c>
       <c r="K572" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.25">
@@ -25395,7 +25536,7 @@
         <v>1404</v>
       </c>
       <c r="K577" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.25">
@@ -25780,7 +25921,7 @@
         <v>1404</v>
       </c>
       <c r="K588" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.25">
@@ -25920,7 +26061,7 @@
         <v>1404</v>
       </c>
       <c r="K592" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.25">
@@ -25990,7 +26131,7 @@
         <v>1404</v>
       </c>
       <c r="K594" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="595" spans="1:11" x14ac:dyDescent="0.25">
@@ -26095,7 +26236,7 @@
         <v>1404</v>
       </c>
       <c r="K597" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.25">
@@ -26165,7 +26306,7 @@
         <v>1404</v>
       </c>
       <c r="K599" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
@@ -26375,7 +26516,7 @@
         <v>1404</v>
       </c>
       <c r="K605" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.25">
@@ -26445,7 +26586,7 @@
         <v>1404</v>
       </c>
       <c r="K607" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.25">
@@ -26585,7 +26726,7 @@
         <v>1404</v>
       </c>
       <c r="K611" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.25">
@@ -26935,7 +27076,7 @@
         <v>1404</v>
       </c>
       <c r="K621" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.25">
@@ -27145,7 +27286,7 @@
         <v>1404</v>
       </c>
       <c r="K627" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.25">
@@ -27670,7 +27811,7 @@
         <v>1404</v>
       </c>
       <c r="K642" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="643" spans="1:11" x14ac:dyDescent="0.25">
@@ -28125,7 +28266,7 @@
         <v>1404</v>
       </c>
       <c r="K655" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="656" spans="1:11" x14ac:dyDescent="0.25">
@@ -28265,7 +28406,7 @@
         <v>1404</v>
       </c>
       <c r="K659" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="660" spans="1:11" x14ac:dyDescent="0.25">
@@ -28580,7 +28721,7 @@
         <v>1404</v>
       </c>
       <c r="K668" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="669" spans="1:11" x14ac:dyDescent="0.25">
@@ -28825,7 +28966,7 @@
         <v>1404</v>
       </c>
       <c r="K675" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="676" spans="1:11" x14ac:dyDescent="0.25">
@@ -28860,7 +29001,7 @@
         <v>1404</v>
       </c>
       <c r="K676" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="677" spans="1:11" x14ac:dyDescent="0.25">
@@ -28965,7 +29106,7 @@
         <v>1404</v>
       </c>
       <c r="K679" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.25">
@@ -29315,7 +29456,7 @@
         <v>1404</v>
       </c>
       <c r="K689" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="690" spans="1:11" x14ac:dyDescent="0.25">
@@ -29945,7 +30086,7 @@
         <v>1404</v>
       </c>
       <c r="K707" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.25">
@@ -30330,7 +30471,7 @@
         <v>1404</v>
       </c>
       <c r="K718" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="719" spans="1:11" x14ac:dyDescent="0.25">
@@ -30645,7 +30786,7 @@
         <v>1404</v>
       </c>
       <c r="K727" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="728" spans="1:11" x14ac:dyDescent="0.25">
@@ -30785,7 +30926,7 @@
         <v>1404</v>
       </c>
       <c r="K731" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="732" spans="1:11" x14ac:dyDescent="0.25">
@@ -31065,7 +31206,7 @@
         <v>1404</v>
       </c>
       <c r="K739" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="740" spans="1:11" x14ac:dyDescent="0.25">
@@ -31205,7 +31346,7 @@
         <v>1404</v>
       </c>
       <c r="K743" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="744" spans="1:11" x14ac:dyDescent="0.25">
@@ -31730,7 +31871,7 @@
         <v>1404</v>
       </c>
       <c r="K758" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="759" spans="1:11" x14ac:dyDescent="0.25">
@@ -32045,7 +32186,7 @@
         <v>1404</v>
       </c>
       <c r="K767" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="768" spans="1:11" x14ac:dyDescent="0.25">
@@ -32255,7 +32396,7 @@
         <v>1404</v>
       </c>
       <c r="K773" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="774" spans="1:11" x14ac:dyDescent="0.25">
@@ -32290,7 +32431,7 @@
         <v>1404</v>
       </c>
       <c r="K774" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="775" spans="1:11" x14ac:dyDescent="0.25">
@@ -32360,7 +32501,7 @@
         <v>1404</v>
       </c>
       <c r="K776" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="777" spans="1:11" x14ac:dyDescent="0.25">
@@ -32430,7 +32571,7 @@
         <v>1404</v>
       </c>
       <c r="K778" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="779" spans="1:11" x14ac:dyDescent="0.25">
@@ -32465,7 +32606,7 @@
         <v>1404</v>
       </c>
       <c r="K779" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="780" spans="1:11" x14ac:dyDescent="0.25">
@@ -32535,7 +32676,7 @@
         <v>1404</v>
       </c>
       <c r="K781" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="782" spans="1:11" x14ac:dyDescent="0.25">
@@ -32570,7 +32711,7 @@
         <v>1404</v>
       </c>
       <c r="K782" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="783" spans="1:11" x14ac:dyDescent="0.25">
@@ -32955,7 +33096,7 @@
         <v>1404</v>
       </c>
       <c r="K793" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="794" spans="1:11" x14ac:dyDescent="0.25">
@@ -33060,7 +33201,7 @@
         <v>1404</v>
       </c>
       <c r="K796" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="797" spans="1:11" x14ac:dyDescent="0.25">
@@ -33305,7 +33446,7 @@
         <v>1404</v>
       </c>
       <c r="K803" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="804" spans="1:11" x14ac:dyDescent="0.25">
@@ -33585,7 +33726,7 @@
         <v>1404</v>
       </c>
       <c r="K811" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="812" spans="1:11" x14ac:dyDescent="0.25">
@@ -33690,7 +33831,7 @@
         <v>1404</v>
       </c>
       <c r="K814" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="815" spans="1:11" x14ac:dyDescent="0.25">
@@ -33760,7 +33901,7 @@
         <v>1404</v>
       </c>
       <c r="K816" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="817" spans="1:11" x14ac:dyDescent="0.25">
@@ -33900,7 +34041,7 @@
         <v>1404</v>
       </c>
       <c r="K820" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="821" spans="1:11" x14ac:dyDescent="0.25">
@@ -34040,7 +34181,7 @@
         <v>1404</v>
       </c>
       <c r="K824" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="825" spans="1:11" x14ac:dyDescent="0.25">
@@ -34075,7 +34216,7 @@
         <v>1404</v>
       </c>
       <c r="K825" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="826" spans="1:11" x14ac:dyDescent="0.25">
@@ -34215,7 +34356,7 @@
         <v>1404</v>
       </c>
       <c r="K829" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="830" spans="1:11" x14ac:dyDescent="0.25">
@@ -34530,7 +34671,7 @@
         <v>1404</v>
       </c>
       <c r="K838" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="839" spans="1:11" x14ac:dyDescent="0.25">
@@ -34845,7 +34986,7 @@
         <v>1404</v>
       </c>
       <c r="K847" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="848" spans="1:11" x14ac:dyDescent="0.25">
@@ -35405,7 +35546,7 @@
         <v>1404</v>
       </c>
       <c r="K863" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="864" spans="1:11" x14ac:dyDescent="0.25">
@@ -35825,7 +35966,7 @@
         <v>1404</v>
       </c>
       <c r="K875" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="876" spans="1:11" x14ac:dyDescent="0.25">
@@ -36245,7 +36386,7 @@
         <v>1404</v>
       </c>
       <c r="K887" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.25">
@@ -36455,7 +36596,7 @@
         <v>1404</v>
       </c>
       <c r="K893" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="894" spans="1:11" x14ac:dyDescent="0.25">
@@ -36525,7 +36666,7 @@
         <v>1404</v>
       </c>
       <c r="K895" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.25">
@@ -36735,7 +36876,7 @@
         <v>1404</v>
       </c>
       <c r="K901" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="902" spans="1:11" x14ac:dyDescent="0.25">
@@ -36840,7 +36981,7 @@
         <v>1404</v>
       </c>
       <c r="K904" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="905" spans="1:11" x14ac:dyDescent="0.25">
@@ -37015,7 +37156,7 @@
         <v>1404</v>
       </c>
       <c r="K909" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="910" spans="1:11" x14ac:dyDescent="0.25">
@@ -37610,7 +37751,7 @@
         <v>1404</v>
       </c>
       <c r="K926" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.25">
@@ -37645,7 +37786,7 @@
         <v>1404</v>
       </c>
       <c r="K927" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.25">
@@ -37680,7 +37821,7 @@
         <v>1404</v>
       </c>
       <c r="K928" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="929" spans="1:11" x14ac:dyDescent="0.25">
@@ -37785,7 +37926,7 @@
         <v>1404</v>
       </c>
       <c r="K931" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="932" spans="1:11" x14ac:dyDescent="0.25">
@@ -37960,7 +38101,7 @@
         <v>1404</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.25">
@@ -38030,7 +38171,7 @@
         <v>1404</v>
       </c>
       <c r="K938" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="939" spans="1:11" x14ac:dyDescent="0.25">
@@ -38310,7 +38451,7 @@
         <v>1404</v>
       </c>
       <c r="K946" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="947" spans="1:11" x14ac:dyDescent="0.25">
@@ -39150,7 +39291,7 @@
         <v>1404</v>
       </c>
       <c r="K970" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="971" spans="1:11" x14ac:dyDescent="0.25">
@@ -39185,7 +39326,7 @@
         <v>1404</v>
       </c>
       <c r="K971" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="972" spans="1:11" x14ac:dyDescent="0.25">
@@ -39920,7 +40061,7 @@
         <v>1404</v>
       </c>
       <c r="K992" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="993" spans="1:11" x14ac:dyDescent="0.25">
@@ -40025,7 +40166,7 @@
         <v>1404</v>
       </c>
       <c r="K995" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="996" spans="1:11" x14ac:dyDescent="0.25">
@@ -40060,7 +40201,7 @@
         <v>1404</v>
       </c>
       <c r="K996" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="997" spans="1:11" x14ac:dyDescent="0.25">
@@ -40235,7 +40376,7 @@
         <v>1404</v>
       </c>
       <c r="K1001" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1002" spans="1:11" x14ac:dyDescent="0.25">
@@ -40305,7 +40446,7 @@
         <v>1404</v>
       </c>
       <c r="K1003" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1004" spans="1:11" x14ac:dyDescent="0.25">
@@ -40410,7 +40551,7 @@
         <v>1404</v>
       </c>
       <c r="K1006" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1007" spans="1:11" x14ac:dyDescent="0.25">
@@ -40865,7 +41006,7 @@
         <v>1404</v>
       </c>
       <c r="K1019" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1020" spans="1:11" x14ac:dyDescent="0.25">
@@ -41425,7 +41566,7 @@
         <v>1404</v>
       </c>
       <c r="K1035" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1036" spans="1:11" x14ac:dyDescent="0.25">
@@ -41530,7 +41671,7 @@
         <v>1404</v>
       </c>
       <c r="K1038" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1039" spans="1:11" x14ac:dyDescent="0.25">
@@ -42020,7 +42161,7 @@
         <v>1404</v>
       </c>
       <c r="K1052" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1053" spans="1:11" x14ac:dyDescent="0.25">
@@ -42265,7 +42406,7 @@
         <v>1404</v>
       </c>
       <c r="K1059" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1060" spans="1:11" x14ac:dyDescent="0.25">
@@ -42895,7 +43036,7 @@
         <v>1404</v>
       </c>
       <c r="K1077" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1078" spans="1:11" x14ac:dyDescent="0.25">
@@ -43420,7 +43561,7 @@
         <v>1404</v>
       </c>
       <c r="K1092" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1093" spans="1:11" x14ac:dyDescent="0.25">
@@ -43840,7 +43981,7 @@
         <v>1404</v>
       </c>
       <c r="K1104" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1105" spans="1:11" x14ac:dyDescent="0.25">
@@ -44225,7 +44366,7 @@
         <v>1404</v>
       </c>
       <c r="K1115" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1116" spans="1:11" x14ac:dyDescent="0.25">
@@ -44260,7 +44401,7 @@
         <v>1404</v>
       </c>
       <c r="K1116" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1117" spans="1:11" x14ac:dyDescent="0.25">
@@ -44400,7 +44541,7 @@
         <v>1404</v>
       </c>
       <c r="K1120" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1121" spans="1:11" x14ac:dyDescent="0.25">
@@ -44540,7 +44681,7 @@
         <v>1404</v>
       </c>
       <c r="K1124" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1125" spans="1:11" x14ac:dyDescent="0.25">
@@ -44925,7 +45066,7 @@
         <v>1404</v>
       </c>
       <c r="K1135" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1136" spans="1:11" x14ac:dyDescent="0.25">
@@ -45065,7 +45206,7 @@
         <v>1404</v>
       </c>
       <c r="K1139" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1140" spans="1:11" x14ac:dyDescent="0.25">
@@ -45100,7 +45241,7 @@
         <v>1404</v>
       </c>
       <c r="K1140" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1141" spans="1:11" x14ac:dyDescent="0.25">
@@ -45170,7 +45311,7 @@
         <v>1404</v>
       </c>
       <c r="K1142" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1143" spans="1:11" x14ac:dyDescent="0.25">
@@ -45205,7 +45346,7 @@
         <v>1404</v>
       </c>
       <c r="K1143" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1144" spans="1:11" x14ac:dyDescent="0.25">
@@ -45240,7 +45381,7 @@
         <v>1404</v>
       </c>
       <c r="K1144" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1145" spans="1:11" x14ac:dyDescent="0.25">
@@ -45590,7 +45731,7 @@
         <v>1404</v>
       </c>
       <c r="K1154" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1155" spans="1:11" x14ac:dyDescent="0.25">
@@ -46395,7 +46536,7 @@
         <v>1404</v>
       </c>
       <c r="K1177" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1178" spans="1:11" x14ac:dyDescent="0.25">
@@ -46815,7 +46956,7 @@
         <v>1404</v>
       </c>
       <c r="K1189" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1190" spans="1:11" x14ac:dyDescent="0.25">
@@ -46920,7 +47061,7 @@
         <v>1404</v>
       </c>
       <c r="K1192" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1193" spans="1:11" x14ac:dyDescent="0.25">
@@ -47130,7 +47271,7 @@
         <v>1405</v>
       </c>
       <c r="K1198" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1199" spans="1:11" x14ac:dyDescent="0.25">
@@ -47165,7 +47306,7 @@
         <v>1405</v>
       </c>
       <c r="K1199" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1200" spans="1:11" x14ac:dyDescent="0.25">
@@ -47200,7 +47341,7 @@
         <v>1405</v>
       </c>
       <c r="K1200" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1201" spans="1:11" x14ac:dyDescent="0.25">
@@ -47235,7 +47376,7 @@
         <v>1405</v>
       </c>
       <c r="K1201" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1202" spans="1:11" x14ac:dyDescent="0.25">
@@ -47270,7 +47411,7 @@
         <v>1405</v>
       </c>
       <c r="K1202" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1203" spans="1:11" x14ac:dyDescent="0.25">
@@ -47445,7 +47586,7 @@
         <v>1404</v>
       </c>
       <c r="K1207" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1208" spans="1:11" x14ac:dyDescent="0.25">
@@ -47550,7 +47691,7 @@
         <v>1404</v>
       </c>
       <c r="K1210" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1211" spans="1:11" x14ac:dyDescent="0.25">
@@ -47655,7 +47796,7 @@
         <v>1405</v>
       </c>
       <c r="K1213" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1214" spans="1:11" x14ac:dyDescent="0.25">
@@ -47690,7 +47831,7 @@
         <v>1405</v>
       </c>
       <c r="K1214" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1215" spans="1:11" x14ac:dyDescent="0.25">
@@ -47725,7 +47866,7 @@
         <v>1405</v>
       </c>
       <c r="K1215" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1216" spans="1:11" x14ac:dyDescent="0.25">
@@ -47760,7 +47901,7 @@
         <v>1405</v>
       </c>
       <c r="K1216" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1217" spans="1:11" x14ac:dyDescent="0.25">
@@ -48250,7 +48391,7 @@
         <v>1404</v>
       </c>
       <c r="K1230" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1231" spans="1:11" x14ac:dyDescent="0.25">
@@ -48285,7 +48426,7 @@
         <v>1405</v>
       </c>
       <c r="K1231" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1232" spans="1:11" x14ac:dyDescent="0.25">
@@ -48320,7 +48461,7 @@
         <v>1404</v>
       </c>
       <c r="K1232" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1233" spans="1:11" x14ac:dyDescent="0.25">
@@ -48355,7 +48496,7 @@
         <v>1405</v>
       </c>
       <c r="K1233" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1234" spans="1:11" x14ac:dyDescent="0.25">
@@ -48460,7 +48601,7 @@
         <v>1404</v>
       </c>
       <c r="K1236" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1237" spans="1:11" x14ac:dyDescent="0.25">
@@ -48565,7 +48706,7 @@
         <v>1404</v>
       </c>
       <c r="K1239" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1240" spans="1:11" x14ac:dyDescent="0.25">
@@ -48600,7 +48741,7 @@
         <v>1404</v>
       </c>
       <c r="K1240" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1241" spans="1:11" x14ac:dyDescent="0.25">
@@ -48670,7 +48811,7 @@
         <v>1404</v>
       </c>
       <c r="K1242" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1243" spans="1:11" x14ac:dyDescent="0.25">
@@ -48740,7 +48881,7 @@
         <v>1404</v>
       </c>
       <c r="K1244" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1245" spans="1:11" x14ac:dyDescent="0.25">
@@ -48950,7 +49091,7 @@
         <v>1404</v>
       </c>
       <c r="K1250" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1251" spans="1:11" x14ac:dyDescent="0.25">
@@ -49090,7 +49231,7 @@
         <v>1405</v>
       </c>
       <c r="K1254" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1255" spans="1:11" x14ac:dyDescent="0.25">
@@ -49125,7 +49266,7 @@
         <v>1405</v>
       </c>
       <c r="K1255" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1256" spans="1:11" x14ac:dyDescent="0.25">
@@ -49160,7 +49301,7 @@
         <v>1405</v>
       </c>
       <c r="K1256" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1257" spans="1:11" x14ac:dyDescent="0.25">
@@ -49650,7 +49791,7 @@
         <v>1405</v>
       </c>
       <c r="K1270" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1271" spans="1:11" x14ac:dyDescent="0.25">
@@ -49685,7 +49826,7 @@
         <v>1405</v>
       </c>
       <c r="K1271" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1272" spans="1:11" x14ac:dyDescent="0.25">
@@ -49720,7 +49861,7 @@
         <v>1405</v>
       </c>
       <c r="K1272" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1273" spans="1:11" x14ac:dyDescent="0.25">
@@ -49825,7 +49966,7 @@
         <v>1405</v>
       </c>
       <c r="K1275" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1276" spans="1:11" x14ac:dyDescent="0.25">
@@ -49860,7 +50001,7 @@
         <v>1405</v>
       </c>
       <c r="K1276" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1277" spans="1:11" x14ac:dyDescent="0.25">
@@ -50070,7 +50211,7 @@
         <v>1405</v>
       </c>
       <c r="K1282" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1283" spans="1:11" x14ac:dyDescent="0.25">
@@ -50105,7 +50246,7 @@
         <v>1405</v>
       </c>
       <c r="K1283" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1284" spans="1:11" x14ac:dyDescent="0.25">
@@ -50140,7 +50281,7 @@
         <v>1405</v>
       </c>
       <c r="K1284" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1285" spans="1:11" x14ac:dyDescent="0.25">
@@ -50175,7 +50316,7 @@
         <v>1405</v>
       </c>
       <c r="K1285" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1286" spans="1:11" x14ac:dyDescent="0.25">
@@ -50210,7 +50351,7 @@
         <v>1405</v>
       </c>
       <c r="K1286" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1287" spans="1:11" x14ac:dyDescent="0.25">
@@ -50245,7 +50386,7 @@
         <v>1405</v>
       </c>
       <c r="K1287" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1288" spans="1:11" x14ac:dyDescent="0.25">
@@ -50280,7 +50421,7 @@
         <v>1405</v>
       </c>
       <c r="K1288" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1289" spans="1:11" x14ac:dyDescent="0.25">
@@ -50315,7 +50456,7 @@
         <v>1405</v>
       </c>
       <c r="K1289" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1290" spans="1:11" x14ac:dyDescent="0.25">
@@ -50350,7 +50491,7 @@
         <v>1405</v>
       </c>
       <c r="K1290" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1291" spans="1:11" x14ac:dyDescent="0.25">
@@ -50385,7 +50526,7 @@
         <v>1405</v>
       </c>
       <c r="K1291" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1292" spans="1:11" x14ac:dyDescent="0.25">
@@ -50420,7 +50561,7 @@
         <v>1405</v>
       </c>
       <c r="K1292" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1293" spans="1:11" x14ac:dyDescent="0.25">
@@ -50455,7 +50596,7 @@
         <v>1405</v>
       </c>
       <c r="K1293" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1294" spans="1:11" x14ac:dyDescent="0.25">
@@ -50490,7 +50631,7 @@
         <v>1405</v>
       </c>
       <c r="K1294" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1295" spans="1:11" x14ac:dyDescent="0.25">
@@ -50525,7 +50666,7 @@
         <v>1405</v>
       </c>
       <c r="K1295" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1296" spans="1:11" x14ac:dyDescent="0.25">
@@ -50560,7 +50701,7 @@
         <v>1405</v>
       </c>
       <c r="K1296" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1297" spans="1:11" x14ac:dyDescent="0.25">
@@ -50595,7 +50736,7 @@
         <v>1405</v>
       </c>
       <c r="K1297" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1298" spans="1:11" x14ac:dyDescent="0.25">
@@ -50630,7 +50771,7 @@
         <v>1405</v>
       </c>
       <c r="K1298" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1299" spans="1:11" x14ac:dyDescent="0.25">
@@ -50665,7 +50806,7 @@
         <v>1405</v>
       </c>
       <c r="K1299" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1300" spans="1:11" x14ac:dyDescent="0.25">
@@ -50700,7 +50841,7 @@
         <v>1405</v>
       </c>
       <c r="K1300" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1301" spans="1:11" x14ac:dyDescent="0.25">
@@ -50723,7 +50864,7 @@
         <v>16</v>
       </c>
       <c r="G1301" s="4" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H1301" s="4" t="s">
         <v>18</v>
@@ -50735,7 +50876,7 @@
         <v>1405</v>
       </c>
       <c r="K1301" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1302" spans="1:11" x14ac:dyDescent="0.25">
@@ -50743,7 +50884,7 @@
         <v>301</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1302" s="4">
         <v>47729</v>
@@ -50758,7 +50899,7 @@
         <v>16</v>
       </c>
       <c r="G1302" s="4" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H1302" s="4" t="s">
         <v>31</v>
@@ -50770,7 +50911,7 @@
         <v>1405</v>
       </c>
       <c r="K1302" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1303" spans="1:11" x14ac:dyDescent="0.25">
@@ -50793,7 +50934,7 @@
         <v>16</v>
       </c>
       <c r="G1303" s="4" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1303" s="4" t="s">
         <v>80</v>
@@ -50805,7 +50946,7 @@
         <v>1405</v>
       </c>
       <c r="K1303" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1304" spans="1:11" x14ac:dyDescent="0.25">
@@ -50822,13 +50963,13 @@
         <v>46141.312245370369</v>
       </c>
       <c r="E1304" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F1304" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1304" s="4" t="s">
         <v>1448</v>
-      </c>
-      <c r="F1304" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1304" s="4" t="s">
-        <v>1449</v>
       </c>
       <c r="H1304" s="4" t="s">
         <v>80</v>
@@ -50840,7 +50981,7 @@
         <v>1405</v>
       </c>
       <c r="K1304" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1305" spans="1:11" x14ac:dyDescent="0.25">
@@ -50863,7 +51004,7 @@
         <v>16</v>
       </c>
       <c r="G1305" s="4" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H1305" s="4" t="s">
         <v>18</v>
@@ -50875,7 +51016,7 @@
         <v>1405</v>
       </c>
       <c r="K1305" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1306" spans="1:11" x14ac:dyDescent="0.25">
@@ -50883,7 +51024,7 @@
         <v>305</v>
       </c>
       <c r="B1306" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1306" s="4">
         <v>23781</v>
@@ -50898,7 +51039,7 @@
         <v>16</v>
       </c>
       <c r="G1306" s="4" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1306" s="4" t="s">
         <v>34</v>
@@ -50910,7 +51051,7 @@
         <v>1405</v>
       </c>
       <c r="K1306" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1307" spans="1:11" x14ac:dyDescent="0.25">
@@ -50918,7 +51059,7 @@
         <v>306</v>
       </c>
       <c r="B1307" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1307" s="4">
         <v>8005323270</v>
@@ -50933,7 +51074,7 @@
         <v>16</v>
       </c>
       <c r="G1307" s="4" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H1307" s="4" t="s">
         <v>18</v>
@@ -50945,7 +51086,7 @@
         <v>1405</v>
       </c>
       <c r="K1307" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1308" spans="1:11" x14ac:dyDescent="0.25">
@@ -50953,7 +51094,7 @@
         <v>307</v>
       </c>
       <c r="B1308" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1308" s="4">
         <v>8005331414</v>
@@ -50968,7 +51109,7 @@
         <v>16</v>
       </c>
       <c r="G1308" s="4" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H1308" s="4" t="s">
         <v>31</v>
@@ -50980,7 +51121,7 @@
         <v>1405</v>
       </c>
       <c r="K1308" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1309" spans="1:11" x14ac:dyDescent="0.25">
@@ -50988,7 +51129,7 @@
         <v>308</v>
       </c>
       <c r="B1309" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1309" s="4">
         <v>8005322828</v>
@@ -51003,7 +51144,7 @@
         <v>16</v>
       </c>
       <c r="G1309" s="4" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H1309" s="4" t="s">
         <v>152</v>
@@ -51015,7 +51156,7 @@
         <v>1405</v>
       </c>
       <c r="K1309" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1310" spans="1:11" x14ac:dyDescent="0.25">
@@ -51038,7 +51179,7 @@
         <v>16</v>
       </c>
       <c r="G1310" s="4" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H1310" s="4" t="s">
         <v>18</v>
@@ -51050,7 +51191,7 @@
         <v>1405</v>
       </c>
       <c r="K1310" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1311" spans="1:11" x14ac:dyDescent="0.25">
@@ -51058,7 +51199,7 @@
         <v>310</v>
       </c>
       <c r="B1311" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1311" s="4">
         <v>1637</v>
@@ -51073,7 +51214,7 @@
         <v>16</v>
       </c>
       <c r="G1311" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H1311" s="4" t="s">
         <v>80</v>
@@ -51085,7 +51226,7 @@
         <v>1405</v>
       </c>
       <c r="K1311" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1312" spans="1:11" x14ac:dyDescent="0.25">
@@ -51093,7 +51234,7 @@
         <v>311</v>
       </c>
       <c r="B1312" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1312" s="4">
         <v>8005267857</v>
@@ -51108,7 +51249,7 @@
         <v>16</v>
       </c>
       <c r="G1312" s="4" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1312" s="4" t="s">
         <v>18</v>
@@ -51120,7 +51261,7 @@
         <v>1405</v>
       </c>
       <c r="K1312" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1313" spans="1:11" x14ac:dyDescent="0.25">
@@ -51143,7 +51284,7 @@
         <v>16</v>
       </c>
       <c r="G1313" s="4" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H1313" s="4" t="s">
         <v>80</v>
@@ -51155,7 +51296,7 @@
         <v>1405</v>
       </c>
       <c r="K1313" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1314" spans="1:11" x14ac:dyDescent="0.25">
@@ -51163,7 +51304,7 @@
         <v>313</v>
       </c>
       <c r="B1314" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1314" s="4">
         <v>8005268010</v>
@@ -51178,7 +51319,7 @@
         <v>16</v>
       </c>
       <c r="G1314" s="4" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H1314" s="4" t="s">
         <v>18</v>
@@ -51190,7 +51331,7 @@
         <v>1405</v>
       </c>
       <c r="K1314" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1315" spans="1:11" x14ac:dyDescent="0.25">
@@ -51198,7 +51339,7 @@
         <v>314</v>
       </c>
       <c r="B1315" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1315" s="4">
         <v>8005262964</v>
@@ -51213,7 +51354,7 @@
         <v>16</v>
       </c>
       <c r="G1315" s="4" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H1315" s="4" t="s">
         <v>18</v>
@@ -51225,7 +51366,7 @@
         <v>1405</v>
       </c>
       <c r="K1315" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1316" spans="1:11" x14ac:dyDescent="0.25">
@@ -51233,7 +51374,7 @@
         <v>315</v>
       </c>
       <c r="B1316" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1316" s="4">
         <v>8005261580</v>
@@ -51248,7 +51389,7 @@
         <v>16</v>
       </c>
       <c r="G1316" s="4" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1316" s="4" t="s">
         <v>80</v>
@@ -51260,7 +51401,7 @@
         <v>1405</v>
       </c>
       <c r="K1316" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1317" spans="1:11" x14ac:dyDescent="0.25">
@@ -51268,7 +51409,7 @@
         <v>316</v>
       </c>
       <c r="B1317" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1317" s="4">
         <v>8005267856</v>
@@ -51283,7 +51424,7 @@
         <v>16</v>
       </c>
       <c r="G1317" s="4" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1317" s="4" t="s">
         <v>18</v>
@@ -51295,7 +51436,7 @@
         <v>1405</v>
       </c>
       <c r="K1317" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1318" spans="1:11" x14ac:dyDescent="0.25">
@@ -51318,7 +51459,7 @@
         <v>16</v>
       </c>
       <c r="G1318" s="4" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H1318" s="4" t="s">
         <v>80</v>
@@ -51330,7 +51471,7 @@
         <v>1405</v>
       </c>
       <c r="K1318" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1319" spans="1:11" x14ac:dyDescent="0.25">
@@ -51338,7 +51479,7 @@
         <v>318</v>
       </c>
       <c r="B1319" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1319" s="4">
         <v>77613</v>
@@ -51350,10 +51491,10 @@
         <v>537</v>
       </c>
       <c r="F1319" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1319" s="4" t="s">
         <v>1465</v>
-      </c>
-      <c r="G1319" s="4" t="s">
-        <v>1466</v>
       </c>
       <c r="H1319" s="4" t="s">
         <v>18</v>
@@ -51365,7 +51506,7 @@
         <v>1405</v>
       </c>
       <c r="K1319" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1320" spans="1:11" x14ac:dyDescent="0.25">
@@ -51373,7 +51514,7 @@
         <v>319</v>
       </c>
       <c r="B1320" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1320" s="4">
         <v>86493</v>
@@ -51385,10 +51526,10 @@
         <v>580</v>
       </c>
       <c r="F1320" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1320" s="4" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H1320" s="4" t="s">
         <v>18</v>
@@ -51400,7 +51541,7 @@
         <v>1405</v>
       </c>
       <c r="K1320" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1321" spans="1:11" x14ac:dyDescent="0.25">
@@ -51408,7 +51549,7 @@
         <v>320</v>
       </c>
       <c r="B1321" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1321" s="4">
         <v>85511</v>
@@ -51417,13 +51558,13 @@
         <v>46205.687384259298</v>
       </c>
       <c r="E1321" s="4" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F1321" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1321" s="4" t="s">
         <v>1468</v>
-      </c>
-      <c r="F1321" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1321" s="4" t="s">
-        <v>1469</v>
       </c>
       <c r="H1321" s="4" t="s">
         <v>31</v>
@@ -51435,7 +51576,7 @@
         <v>1405</v>
       </c>
       <c r="K1321" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1322" spans="1:11" x14ac:dyDescent="0.25">
@@ -51443,7 +51584,7 @@
         <v>321</v>
       </c>
       <c r="B1322" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1322" s="4">
         <v>87456</v>
@@ -51455,10 +51596,10 @@
         <v>1246</v>
       </c>
       <c r="F1322" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1322" s="4" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H1322" s="4" t="s">
         <v>18</v>
@@ -51470,7 +51611,7 @@
         <v>1405</v>
       </c>
       <c r="K1322" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1323" spans="1:11" x14ac:dyDescent="0.25">
@@ -51478,7 +51619,7 @@
         <v>322</v>
       </c>
       <c r="B1323" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1323" s="4">
         <v>84877</v>
@@ -51490,10 +51631,10 @@
         <v>1252</v>
       </c>
       <c r="F1323" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1323" s="4" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H1323" s="4" t="s">
         <v>80</v>
@@ -51505,7 +51646,7 @@
         <v>1405</v>
       </c>
       <c r="K1323" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1324" spans="1:11" x14ac:dyDescent="0.25">
@@ -51513,7 +51654,7 @@
         <v>323</v>
       </c>
       <c r="B1324" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1324" s="4">
         <v>88457</v>
@@ -51525,10 +51666,10 @@
         <v>1413</v>
       </c>
       <c r="F1324" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1324" s="4" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H1324" s="4" t="s">
         <v>18</v>
@@ -51540,7 +51681,7 @@
         <v>1405</v>
       </c>
       <c r="K1324" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1325" spans="1:11" x14ac:dyDescent="0.25">
@@ -51560,10 +51701,10 @@
         <v>1427</v>
       </c>
       <c r="F1325" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1325" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H1325" s="4" t="s">
         <v>18</v>
@@ -51575,7 +51716,7 @@
         <v>1405</v>
       </c>
       <c r="K1325" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1326" spans="1:11" x14ac:dyDescent="0.25">
@@ -51592,13 +51733,13 @@
         <v>46209.3108333333</v>
       </c>
       <c r="E1326" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F1326" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1326" s="4" t="s">
         <v>1474</v>
-      </c>
-      <c r="F1326" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1326" s="4" t="s">
-        <v>1475</v>
       </c>
       <c r="H1326" s="4" t="s">
         <v>80</v>
@@ -51610,7 +51751,7 @@
         <v>1405</v>
       </c>
       <c r="K1326" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1327" spans="1:11" x14ac:dyDescent="0.25">
@@ -51618,7 +51759,7 @@
         <v>326</v>
       </c>
       <c r="B1327" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1327" s="4">
         <v>91153</v>
@@ -51630,10 +51771,10 @@
         <v>1242</v>
       </c>
       <c r="F1327" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1327" s="4" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H1327" s="4" t="s">
         <v>18</v>
@@ -51645,7 +51786,7 @@
         <v>1405</v>
       </c>
       <c r="K1327" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1328" spans="1:11" x14ac:dyDescent="0.25">
@@ -51665,10 +51806,10 @@
         <v>1248</v>
       </c>
       <c r="F1328" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1328" s="4" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H1328" s="4" t="s">
         <v>13</v>
@@ -51680,7 +51821,7 @@
         <v>1405</v>
       </c>
       <c r="K1328" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1329" spans="1:11" x14ac:dyDescent="0.25">
@@ -51688,7 +51829,7 @@
         <v>328</v>
       </c>
       <c r="B1329" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1329" s="4">
         <v>91068</v>
@@ -51700,10 +51841,10 @@
         <v>580</v>
       </c>
       <c r="F1329" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1329" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H1329" s="4" t="s">
         <v>18</v>
@@ -51715,7 +51856,7 @@
         <v>1405</v>
       </c>
       <c r="K1329" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1330" spans="1:11" x14ac:dyDescent="0.25">
@@ -51732,13 +51873,13 @@
         <v>46209.405763888899</v>
       </c>
       <c r="E1330" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F1330" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1330" s="4" t="s">
         <v>1479</v>
-      </c>
-      <c r="F1330" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1330" s="4" t="s">
-        <v>1480</v>
       </c>
       <c r="H1330" s="4" t="s">
         <v>18</v>
@@ -51750,7 +51891,7 @@
         <v>1405</v>
       </c>
       <c r="K1330" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1331" spans="1:11" x14ac:dyDescent="0.25">
@@ -51758,7 +51899,7 @@
         <v>330</v>
       </c>
       <c r="B1331" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1331" s="4">
         <v>88667</v>
@@ -51767,13 +51908,13 @@
         <v>46209.555567129602</v>
       </c>
       <c r="E1331" s="4" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F1331" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1331" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H1331" s="4" t="s">
         <v>18</v>
@@ -51785,7 +51926,7 @@
         <v>1405</v>
       </c>
       <c r="K1331" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1332" spans="1:11" x14ac:dyDescent="0.25">
@@ -51805,10 +51946,10 @@
         <v>1252</v>
       </c>
       <c r="F1332" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1332" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H1332" s="4" t="s">
         <v>18</v>
@@ -51820,7 +51961,7 @@
         <v>1405</v>
       </c>
       <c r="K1332" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1333" spans="1:11" x14ac:dyDescent="0.25">
@@ -51840,10 +51981,10 @@
         <v>1242</v>
       </c>
       <c r="F1333" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1333" s="4" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H1333" s="4" t="s">
         <v>18</v>
@@ -51855,7 +51996,7 @@
         <v>1405</v>
       </c>
       <c r="K1333" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1334" spans="1:11" x14ac:dyDescent="0.25">
@@ -51875,10 +52016,10 @@
         <v>1246</v>
       </c>
       <c r="F1334" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1334" s="4" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H1334" s="4" t="s">
         <v>13</v>
@@ -51890,7 +52031,7 @@
         <v>1405</v>
       </c>
       <c r="K1334" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1335" spans="1:11" x14ac:dyDescent="0.25">
@@ -51907,13 +52048,13 @@
         <v>46210.397152777798</v>
       </c>
       <c r="E1335" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F1335" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1335" s="4" t="s">
         <v>1485</v>
-      </c>
-      <c r="F1335" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1335" s="4" t="s">
-        <v>1486</v>
       </c>
       <c r="H1335" s="4" t="s">
         <v>80</v>
@@ -51925,7 +52066,7 @@
         <v>1405</v>
       </c>
       <c r="K1335" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1336" spans="1:11" x14ac:dyDescent="0.25">
@@ -51933,7 +52074,7 @@
         <v>335</v>
       </c>
       <c r="B1336" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1336" s="4">
         <v>88352</v>
@@ -51945,10 +52086,10 @@
         <v>537</v>
       </c>
       <c r="F1336" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1336" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H1336" s="4" t="s">
         <v>18</v>
@@ -51960,7 +52101,7 @@
         <v>1405</v>
       </c>
       <c r="K1336" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1337" spans="1:11" x14ac:dyDescent="0.25">
@@ -51977,13 +52118,13 @@
         <v>46211.625416666699</v>
       </c>
       <c r="E1337" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F1337" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1337" s="4" t="s">
         <v>1488</v>
-      </c>
-      <c r="F1337" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1337" s="4" t="s">
-        <v>1489</v>
       </c>
       <c r="H1337" s="4" t="s">
         <v>18</v>
@@ -51995,7 +52136,7 @@
         <v>1405</v>
       </c>
       <c r="K1337" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1338" spans="1:11" x14ac:dyDescent="0.25">
@@ -52003,7 +52144,7 @@
         <v>337</v>
       </c>
       <c r="B1338" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1338" s="4">
         <v>86122</v>
@@ -52015,10 +52156,10 @@
         <v>1248</v>
       </c>
       <c r="F1338" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1338" s="4" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H1338" s="4" t="s">
         <v>34</v>
@@ -52030,7 +52171,7 @@
         <v>1405</v>
       </c>
       <c r="K1338" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1339" spans="1:11" x14ac:dyDescent="0.25">
@@ -52038,7 +52179,7 @@
         <v>338</v>
       </c>
       <c r="B1339" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1339" s="4">
         <v>88500</v>
@@ -52047,13 +52188,13 @@
         <v>46211.718460648197</v>
       </c>
       <c r="E1339" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1339" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1339" s="4" t="s">
         <v>1491</v>
-      </c>
-      <c r="F1339" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1339" s="4" t="s">
-        <v>1492</v>
       </c>
       <c r="H1339" s="4" t="s">
         <v>34</v>
@@ -52065,7 +52206,7 @@
         <v>1405</v>
       </c>
       <c r="K1339" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1340" spans="1:11" x14ac:dyDescent="0.25">
@@ -52073,7 +52214,7 @@
         <v>339</v>
       </c>
       <c r="B1340" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1340" s="4">
         <v>91901</v>
@@ -52085,10 +52226,10 @@
         <v>1430</v>
       </c>
       <c r="F1340" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1340" s="4" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H1340" s="4" t="s">
         <v>152</v>
@@ -52100,7 +52241,7 @@
         <v>1405</v>
       </c>
       <c r="K1340" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1341" spans="1:11" x14ac:dyDescent="0.25">
@@ -52108,7 +52249,7 @@
         <v>340</v>
       </c>
       <c r="B1341" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1341" s="4">
         <v>90803</v>
@@ -52120,10 +52261,10 @@
         <v>577</v>
       </c>
       <c r="F1341" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1341" s="4" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H1341" s="4" t="s">
         <v>34</v>
@@ -52135,7 +52276,7 @@
         <v>1405</v>
       </c>
       <c r="K1341" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1342" spans="1:11" x14ac:dyDescent="0.25">
@@ -52155,10 +52296,10 @@
         <v>1413</v>
       </c>
       <c r="F1342" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1342" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H1342" s="4" t="s">
         <v>18</v>
@@ -52170,7 +52311,7 @@
         <v>1405</v>
       </c>
       <c r="K1342" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1343" spans="1:11" x14ac:dyDescent="0.25">
@@ -52178,7 +52319,7 @@
         <v>342</v>
       </c>
       <c r="B1343" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1343" s="4">
         <v>95091</v>
@@ -52190,10 +52331,10 @@
         <v>1256</v>
       </c>
       <c r="F1343" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1343" s="4" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H1343" s="4" t="s">
         <v>152</v>
@@ -52205,7 +52346,7 @@
         <v>1405</v>
       </c>
       <c r="K1343" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1344" spans="1:11" x14ac:dyDescent="0.25">
@@ -52213,7 +52354,7 @@
         <v>343</v>
       </c>
       <c r="B1344" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1344" s="4">
         <v>94455</v>
@@ -52225,10 +52366,10 @@
         <v>580</v>
       </c>
       <c r="F1344" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1344" s="4" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H1344" s="4" t="s">
         <v>18</v>
@@ -52240,7 +52381,7 @@
         <v>1405</v>
       </c>
       <c r="K1344" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1345" spans="1:11" x14ac:dyDescent="0.25">
@@ -52257,13 +52398,13 @@
         <v>46213.467465277798</v>
       </c>
       <c r="E1345" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F1345" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1345" s="4" t="s">
         <v>1498</v>
-      </c>
-      <c r="F1345" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1345" s="4" t="s">
-        <v>1499</v>
       </c>
       <c r="H1345" s="4" t="s">
         <v>18</v>
@@ -52275,7 +52416,7 @@
         <v>1405</v>
       </c>
       <c r="K1345" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1346" spans="1:11" x14ac:dyDescent="0.25">
@@ -52283,7 +52424,7 @@
         <v>345</v>
       </c>
       <c r="B1346" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1346" s="4">
         <v>92666</v>
@@ -52295,10 +52436,10 @@
         <v>1246</v>
       </c>
       <c r="F1346" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1346" s="4" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H1346" s="4" t="s">
         <v>31</v>
@@ -52310,7 +52451,7 @@
         <v>1405</v>
       </c>
       <c r="K1346" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1347" spans="1:11" x14ac:dyDescent="0.25">
@@ -52318,7 +52459,7 @@
         <v>346</v>
       </c>
       <c r="B1347" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1347" s="4">
         <v>92151</v>
@@ -52330,10 +52471,10 @@
         <v>543</v>
       </c>
       <c r="F1347" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1347" s="4" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H1347" s="4" t="s">
         <v>18</v>
@@ -52345,7 +52486,7 @@
         <v>1405</v>
       </c>
       <c r="K1347" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1348" spans="1:11" x14ac:dyDescent="0.25">
@@ -52353,7 +52494,7 @@
         <v>347</v>
       </c>
       <c r="B1348" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1348" s="4">
         <v>80778</v>
@@ -52362,13 +52503,13 @@
         <v>46214.486516203702</v>
       </c>
       <c r="E1348" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F1348" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1348" s="4" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H1348" s="4" t="s">
         <v>13</v>
@@ -52380,7 +52521,7 @@
         <v>1405</v>
       </c>
       <c r="K1348" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1349" spans="1:11" x14ac:dyDescent="0.25">
@@ -52400,10 +52541,10 @@
         <v>1248</v>
       </c>
       <c r="F1349" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1349" s="4" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H1349" s="4" t="s">
         <v>34</v>
@@ -52415,7 +52556,7 @@
         <v>1405</v>
       </c>
       <c r="K1349" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1350" spans="1:11" x14ac:dyDescent="0.25">
@@ -52435,10 +52576,10 @@
         <v>1246</v>
       </c>
       <c r="F1350" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1350" s="4" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H1350" s="4" t="s">
         <v>18</v>
@@ -52450,7 +52591,7 @@
         <v>1405</v>
       </c>
       <c r="K1350" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1351" spans="1:11" x14ac:dyDescent="0.25">
@@ -52458,7 +52599,7 @@
         <v>350</v>
       </c>
       <c r="B1351" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1351" s="4">
         <v>87232</v>
@@ -52470,10 +52611,10 @@
         <v>1413</v>
       </c>
       <c r="F1351" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1351" s="4" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H1351" s="4" t="s">
         <v>31</v>
@@ -52485,7 +52626,7 @@
         <v>1405</v>
       </c>
       <c r="K1351" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1352" spans="1:11" x14ac:dyDescent="0.25">
@@ -52505,10 +52646,10 @@
         <v>580</v>
       </c>
       <c r="F1352" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1352" s="4" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H1352" s="4" t="s">
         <v>18</v>
@@ -52520,7 +52661,7 @@
         <v>1405</v>
       </c>
       <c r="K1352" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1353" spans="1:11" x14ac:dyDescent="0.25">
@@ -52528,7 +52669,7 @@
         <v>352</v>
       </c>
       <c r="B1353" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1353" s="4">
         <v>91804</v>
@@ -52540,10 +52681,10 @@
         <v>1244</v>
       </c>
       <c r="F1353" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1353" s="4" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H1353" s="4" t="s">
         <v>34</v>
@@ -52555,7 +52696,7 @@
         <v>1405</v>
       </c>
       <c r="K1353" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1354" spans="1:11" x14ac:dyDescent="0.25">
@@ -52575,10 +52716,10 @@
         <v>541</v>
       </c>
       <c r="F1354" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1354" s="4" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H1354" s="4" t="s">
         <v>34</v>
@@ -52590,7 +52731,7 @@
         <v>1405</v>
       </c>
       <c r="K1354" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1355" spans="1:11" x14ac:dyDescent="0.25">
@@ -52607,13 +52748,13 @@
         <v>46216.589780092603</v>
       </c>
       <c r="E1355" s="4" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F1355" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1355" s="4" t="s">
         <v>1509</v>
-      </c>
-      <c r="F1355" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1355" s="4" t="s">
-        <v>1510</v>
       </c>
       <c r="H1355" s="4" t="s">
         <v>18</v>
@@ -52625,7 +52766,7 @@
         <v>1405</v>
       </c>
       <c r="K1355" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1356" spans="1:11" x14ac:dyDescent="0.25">
@@ -52645,10 +52786,10 @@
         <v>1244</v>
       </c>
       <c r="F1356" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1356" s="4" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H1356" s="4" t="s">
         <v>18</v>
@@ -52660,7 +52801,7 @@
         <v>1405</v>
       </c>
       <c r="K1356" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1357" spans="1:11" x14ac:dyDescent="0.25">
@@ -52668,7 +52809,7 @@
         <v>356</v>
       </c>
       <c r="B1357" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1357" s="4">
         <v>85506</v>
@@ -52680,10 +52821,10 @@
         <v>1242</v>
       </c>
       <c r="F1357" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1357" s="4" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H1357" s="4" t="s">
         <v>18</v>
@@ -52695,7 +52836,7 @@
         <v>1405</v>
       </c>
       <c r="K1357" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1358" spans="1:11" x14ac:dyDescent="0.25">
@@ -52715,10 +52856,10 @@
         <v>577</v>
       </c>
       <c r="F1358" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1358" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H1358" s="4" t="s">
         <v>18</v>
@@ -52730,7 +52871,7 @@
         <v>1405</v>
       </c>
       <c r="K1358" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1359" spans="1:11" x14ac:dyDescent="0.25">
@@ -52750,10 +52891,10 @@
         <v>1416</v>
       </c>
       <c r="F1359" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1359" s="4" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H1359" s="4" t="s">
         <v>80</v>
@@ -52765,7 +52906,7 @@
         <v>1405</v>
       </c>
       <c r="K1359" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1360" spans="1:11" x14ac:dyDescent="0.25">
@@ -52773,7 +52914,7 @@
         <v>359</v>
       </c>
       <c r="B1360" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1360" s="4">
         <v>96993</v>
@@ -52785,10 +52926,10 @@
         <v>577</v>
       </c>
       <c r="F1360" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1360" s="4" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H1360" s="4" t="s">
         <v>18</v>
@@ -52800,7 +52941,7 @@
         <v>1405</v>
       </c>
       <c r="K1360" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1361" spans="1:11" x14ac:dyDescent="0.25">
@@ -52808,7 +52949,7 @@
         <v>360</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1361" s="4">
         <v>94534</v>
@@ -52820,10 +52961,10 @@
         <v>1413</v>
       </c>
       <c r="F1361" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1361" s="4" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H1361" s="4" t="s">
         <v>31</v>
@@ -52835,7 +52976,7 @@
         <v>1405</v>
       </c>
       <c r="K1361" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1362" spans="1:11" x14ac:dyDescent="0.25">
@@ -52843,7 +52984,7 @@
         <v>361</v>
       </c>
       <c r="B1362" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1362" s="4">
         <v>94778</v>
@@ -52855,10 +52996,10 @@
         <v>1416</v>
       </c>
       <c r="F1362" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1362" s="4" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H1362" s="4" t="s">
         <v>31</v>
@@ -52870,7 +53011,7 @@
         <v>1405</v>
       </c>
       <c r="K1362" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1363" spans="1:11" x14ac:dyDescent="0.25">
@@ -52878,7 +53019,7 @@
         <v>362</v>
       </c>
       <c r="B1363" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1363" s="4">
         <v>97056</v>
@@ -52890,10 +53031,10 @@
         <v>1242</v>
       </c>
       <c r="F1363" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1363" s="4" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H1363" s="4" t="s">
         <v>18</v>
@@ -52905,7 +53046,7 @@
         <v>1405</v>
       </c>
       <c r="K1363" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1364" spans="1:11" x14ac:dyDescent="0.25">
@@ -52922,13 +53063,13 @@
         <v>46218.373020833344</v>
       </c>
       <c r="E1364" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F1364" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1364" s="4" t="s">
         <v>1519</v>
-      </c>
-      <c r="F1364" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1364" s="4" t="s">
-        <v>1520</v>
       </c>
       <c r="H1364" s="4" t="s">
         <v>18</v>
@@ -52940,7 +53081,7 @@
         <v>1405</v>
       </c>
       <c r="K1364" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1365" spans="1:11" x14ac:dyDescent="0.25">
@@ -52957,13 +53098,13 @@
         <v>46218.758553240739</v>
       </c>
       <c r="E1365" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F1365" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1365" s="4" t="s">
         <v>1521</v>
-      </c>
-      <c r="F1365" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1365" s="4" t="s">
-        <v>1522</v>
       </c>
       <c r="H1365" s="4" t="s">
         <v>18</v>
@@ -52975,7 +53116,7 @@
         <v>1405</v>
       </c>
       <c r="K1365" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1366" spans="1:11" x14ac:dyDescent="0.25">
@@ -52995,10 +53136,10 @@
         <v>537</v>
       </c>
       <c r="F1366" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1366" s="4" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H1366" s="4" t="s">
         <v>18</v>
@@ -53010,7 +53151,7 @@
         <v>1405</v>
       </c>
       <c r="K1366" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1367" spans="1:11" x14ac:dyDescent="0.25">
@@ -53027,13 +53168,13 @@
         <v>46220.267152777778</v>
       </c>
       <c r="E1367" s="4" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F1367" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1367" s="4" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H1367" s="4" t="s">
         <v>34</v>
@@ -53045,7 +53186,7 @@
         <v>1405</v>
       </c>
       <c r="K1367" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1368" spans="1:11" x14ac:dyDescent="0.25">
@@ -53065,10 +53206,10 @@
         <v>1430</v>
       </c>
       <c r="F1368" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1368" s="4" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H1368" s="4" t="s">
         <v>13</v>
@@ -53080,7 +53221,7 @@
         <v>1405</v>
       </c>
       <c r="K1368" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1369" spans="1:11" x14ac:dyDescent="0.25">
@@ -53097,13 +53238,13 @@
         <v>46220.35869212963</v>
       </c>
       <c r="E1369" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F1369" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1369" s="4" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H1369" s="4" t="s">
         <v>18</v>
@@ -53115,7 +53256,7 @@
         <v>1405</v>
       </c>
       <c r="K1369" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1370" spans="1:11" x14ac:dyDescent="0.25">
@@ -53132,13 +53273,13 @@
         <v>46221.760682870372</v>
       </c>
       <c r="E1370" s="4" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F1370" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1370" s="4" t="s">
         <v>1540</v>
-      </c>
-      <c r="F1370" s="4" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G1370" s="4" t="s">
-        <v>1541</v>
       </c>
       <c r="H1370" s="4" t="s">
         <v>18</v>
@@ -53147,10 +53288,10 @@
         <v>50</v>
       </c>
       <c r="J1370" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1370" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1371" spans="1:11" x14ac:dyDescent="0.25">
@@ -53170,10 +53311,10 @@
         <v>537</v>
       </c>
       <c r="F1371" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1371" s="4" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H1371" s="4" t="s">
         <v>18</v>
@@ -53182,10 +53323,10 @@
         <v>59</v>
       </c>
       <c r="J1371" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1371" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1372" spans="1:11" x14ac:dyDescent="0.25">
@@ -53193,7 +53334,7 @@
         <v>371</v>
       </c>
       <c r="B1372" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1372" s="4">
         <v>98261</v>
@@ -53205,10 +53346,10 @@
         <v>1252</v>
       </c>
       <c r="F1372" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1372" s="4" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H1372" s="4" t="s">
         <v>13</v>
@@ -53217,10 +53358,10 @@
         <v>26</v>
       </c>
       <c r="J1372" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1372" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1373" spans="1:11" x14ac:dyDescent="0.25">
@@ -53228,7 +53369,7 @@
         <v>372</v>
       </c>
       <c r="B1373" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1373" s="4">
         <v>100121</v>
@@ -53240,10 +53381,10 @@
         <v>803</v>
       </c>
       <c r="F1373" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1373" s="4" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H1373" s="4" t="s">
         <v>13</v>
@@ -53252,10 +53393,10 @@
         <v>26</v>
       </c>
       <c r="J1373" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1373" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1374" spans="1:11" x14ac:dyDescent="0.25">
@@ -53275,10 +53416,10 @@
         <v>1242</v>
       </c>
       <c r="F1374" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1374" s="4" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H1374" s="4" t="s">
         <v>18</v>
@@ -53287,10 +53428,10 @@
         <v>1010</v>
       </c>
       <c r="J1374" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1374" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1375" spans="1:11" x14ac:dyDescent="0.25">
@@ -53310,10 +53451,10 @@
         <v>1248</v>
       </c>
       <c r="F1375" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1375" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H1375" s="4" t="s">
         <v>18</v>
@@ -53322,10 +53463,10 @@
         <v>1010</v>
       </c>
       <c r="J1375" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1375" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1376" spans="1:11" x14ac:dyDescent="0.25">
@@ -53333,7 +53474,7 @@
         <v>375</v>
       </c>
       <c r="B1376" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1376" s="4">
         <v>94295</v>
@@ -53345,10 +53486,10 @@
         <v>1246</v>
       </c>
       <c r="F1376" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1376" s="4" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H1376" s="4" t="s">
         <v>31</v>
@@ -53357,10 +53498,10 @@
         <v>32</v>
       </c>
       <c r="J1376" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1376" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1377" spans="1:11" x14ac:dyDescent="0.25">
@@ -53377,13 +53518,13 @@
         <v>46224.304930555547</v>
       </c>
       <c r="E1377" s="4" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F1377" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1377" s="4" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H1377" s="4" t="s">
         <v>18</v>
@@ -53392,10 +53533,10 @@
         <v>1010</v>
       </c>
       <c r="J1377" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1377" s="4" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1378" spans="1:11" x14ac:dyDescent="0.25">
@@ -53403,7 +53544,7 @@
         <v>377</v>
       </c>
       <c r="B1378" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1378" s="4">
         <v>92473</v>
@@ -53415,10 +53556,10 @@
         <v>1242</v>
       </c>
       <c r="F1378" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1378" s="4" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H1378" s="4" t="s">
         <v>80</v>
@@ -53427,10 +53568,10 @@
         <v>81</v>
       </c>
       <c r="J1378" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1378" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1379" spans="1:11" x14ac:dyDescent="0.25">
@@ -53438,7 +53579,7 @@
         <v>378</v>
       </c>
       <c r="B1379" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1379" s="4">
         <v>86207</v>
@@ -53447,13 +53588,13 @@
         <v>46224.442812499998</v>
       </c>
       <c r="E1379" s="4" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F1379" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1379" s="4" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H1379" s="4" t="s">
         <v>80</v>
@@ -53462,10 +53603,10 @@
         <v>151</v>
       </c>
       <c r="J1379" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1379" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1380" spans="1:11" x14ac:dyDescent="0.25">
@@ -53485,10 +53626,10 @@
         <v>1242</v>
       </c>
       <c r="F1380" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1380" s="4" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H1380" s="4" t="s">
         <v>18</v>
@@ -53497,10 +53638,10 @@
         <v>1010</v>
       </c>
       <c r="J1380" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1380" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1381" spans="1:11" x14ac:dyDescent="0.25">
@@ -53520,22 +53661,22 @@
         <v>1416</v>
       </c>
       <c r="F1381" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1381" s="4" t="s">
+        <v>1533</v>
+      </c>
+      <c r="H1381" s="4" t="s">
         <v>1534</v>
       </c>
-      <c r="H1381" s="4" t="s">
+      <c r="I1381" s="4" t="s">
         <v>1535</v>
       </c>
-      <c r="I1381" s="4" t="s">
-        <v>1536</v>
-      </c>
       <c r="J1381" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1381" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1382" spans="1:11" x14ac:dyDescent="0.25">
@@ -53543,7 +53684,7 @@
         <v>381</v>
       </c>
       <c r="B1382" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C1382" s="4">
         <v>93985</v>
@@ -53552,13 +53693,13 @@
         <v>46224.674560185187</v>
       </c>
       <c r="E1382" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F1382" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1382" s="4" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H1382" s="4" t="s">
         <v>34</v>
@@ -53567,10 +53708,10 @@
         <v>98</v>
       </c>
       <c r="J1382" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1382" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1383" spans="1:11" x14ac:dyDescent="0.25">
@@ -53587,13 +53728,13 @@
         <v>46224.779664351852</v>
       </c>
       <c r="E1383" s="4" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F1383" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1383" s="4" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H1383" s="4" t="s">
         <v>18</v>
@@ -53602,10 +53743,10 @@
         <v>1010</v>
       </c>
       <c r="J1383" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1383" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1384" spans="1:11" x14ac:dyDescent="0.25">
@@ -53622,13 +53763,13 @@
         <v>46224.894201388888</v>
       </c>
       <c r="E1384" s="4" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F1384" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G1384" s="4" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H1384" s="4" t="s">
         <v>18</v>
@@ -53637,9 +53778,1056 @@
         <v>50</v>
       </c>
       <c r="J1384" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K1384" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1385" s="4">
+        <v>387</v>
+      </c>
+      <c r="B1385" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1385" s="4">
+        <v>85699</v>
+      </c>
+      <c r="D1385" s="2">
+        <v>46226.303622685176</v>
+      </c>
+      <c r="E1385" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1385" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1385" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="H1385" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1385" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1385" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1385" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1386" s="4">
+        <v>389</v>
+      </c>
+      <c r="B1386" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1386" s="4">
+        <v>79599</v>
+      </c>
+      <c r="D1386" s="2">
+        <v>46226.464259259257</v>
+      </c>
+      <c r="E1386" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1386" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1386" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="H1386" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1386" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1386" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1386" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1387" s="4">
+        <v>390</v>
+      </c>
+      <c r="B1387" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1387" s="4">
+        <v>101958</v>
+      </c>
+      <c r="D1387" s="2">
+        <v>46227.313773148147</v>
+      </c>
+      <c r="E1387" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="F1387" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1387" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H1387" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1387" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1387" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1387" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1388" s="4">
+        <v>391</v>
+      </c>
+      <c r="B1388" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1388" s="4">
+        <v>91490</v>
+      </c>
+      <c r="D1388" s="2">
+        <v>46227.535555555558</v>
+      </c>
+      <c r="E1388" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1388" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1388" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="H1388" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1388" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1388" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1388" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1389" s="4">
+        <v>392</v>
+      </c>
+      <c r="B1389" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1389" s="4">
+        <v>103497</v>
+      </c>
+      <c r="D1389" s="2">
+        <v>46230.163402777784</v>
+      </c>
+      <c r="E1389" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1389" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1389" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H1389" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1389" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="J1389" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1389" s="4" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1390" s="4">
+        <v>393</v>
+      </c>
+      <c r="B1390" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1390" s="4">
+        <v>90234</v>
+      </c>
+      <c r="D1390" s="2">
+        <v>46230.252002314817</v>
+      </c>
+      <c r="E1390" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1390" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1390" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H1390" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1390" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1390" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1390" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1391" s="4">
+        <v>394</v>
+      </c>
+      <c r="B1391" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1391" s="4">
+        <v>103674</v>
+      </c>
+      <c r="D1391" s="2">
+        <v>46230.269479166673</v>
+      </c>
+      <c r="E1391" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1391" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1391" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H1391" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1391" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1391" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1391" s="4" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1392" s="4">
+        <v>395</v>
+      </c>
+      <c r="B1392" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1392" s="4">
+        <v>103554</v>
+      </c>
+      <c r="D1392" s="2">
+        <v>46230.353437500002</v>
+      </c>
+      <c r="E1392" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1392" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1392" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="H1392" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1392" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1392" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1392" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1393" s="4">
+        <v>396</v>
+      </c>
+      <c r="B1393" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C1393" s="4">
+        <v>106661</v>
+      </c>
+      <c r="D1393" s="2">
+        <v>46230.440486111111</v>
+      </c>
+      <c r="E1393" s="4" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F1393" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1393" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H1393" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1393" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1393" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1393" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1394" s="4">
+        <v>397</v>
+      </c>
+      <c r="B1394" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1394" s="4">
+        <v>100515</v>
+      </c>
+      <c r="D1394" s="2">
+        <v>46230.499502314808</v>
+      </c>
+      <c r="E1394" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1394" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1394" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="H1394" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1394" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1394" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1394" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1395" s="4">
+        <v>398</v>
+      </c>
+      <c r="B1395" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1395" s="4">
+        <v>106143</v>
+      </c>
+      <c r="D1395" s="2">
+        <v>46230.517500000002</v>
+      </c>
+      <c r="E1395" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1395" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1395" s="4" t="s">
+        <v>1560</v>
+      </c>
+      <c r="H1395" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="I1395" s="4" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J1395" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1395" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1396" s="4">
+        <v>400</v>
+      </c>
+      <c r="B1396" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1396" s="4">
+        <v>106365</v>
+      </c>
+      <c r="D1396" s="2">
+        <v>46231.378865740742</v>
+      </c>
+      <c r="E1396" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F1396" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1396" s="4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="H1396" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1396" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1396" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1396" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1397" s="4">
+        <v>401</v>
+      </c>
+      <c r="B1397" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1397" s="4">
+        <v>91356</v>
+      </c>
+      <c r="D1397" s="2">
+        <v>46231.618923611109</v>
+      </c>
+      <c r="E1397" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F1397" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1397" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H1397" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1397" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1397" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1397" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1398" s="4">
+        <v>402</v>
+      </c>
+      <c r="B1398" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1398" s="4">
+        <v>106419</v>
+      </c>
+      <c r="D1398" s="2">
+        <v>46232.304594907408</v>
+      </c>
+      <c r="E1398" s="4" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F1398" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1398" s="4" t="s">
+        <v>1565</v>
+      </c>
+      <c r="H1398" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1398" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1398" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1398" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1399" s="4">
+        <v>403</v>
+      </c>
+      <c r="B1399" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1399" s="4">
+        <v>96662</v>
+      </c>
+      <c r="D1399" s="2">
+        <v>46232.311030092591</v>
+      </c>
+      <c r="E1399" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1399" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1399" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H1399" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="I1399" s="4" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J1399" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1399" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1400" s="4">
+        <v>404</v>
+      </c>
+      <c r="B1400" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1400" s="4">
+        <v>98899</v>
+      </c>
+      <c r="D1400" s="2">
+        <v>46232.558495370373</v>
+      </c>
+      <c r="E1400" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1400" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1400" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="H1400" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1400" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1400" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1400" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1401" s="4">
+        <v>405</v>
+      </c>
+      <c r="B1401" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1401" s="4">
+        <v>104621</v>
+      </c>
+      <c r="D1401" s="2">
+        <v>46233.339548611111</v>
+      </c>
+      <c r="E1401" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1401" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1401" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H1401" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1401" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="J1401" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1401" s="4" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1402" s="4">
+        <v>406</v>
+      </c>
+      <c r="B1402" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1402" s="4">
+        <v>77825</v>
+      </c>
+      <c r="D1402" s="2">
+        <v>46233.38753472222</v>
+      </c>
+      <c r="E1402" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F1402" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1402" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="H1402" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1402" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1402" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1402" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1403" s="4">
+        <v>407</v>
+      </c>
+      <c r="B1403" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1403" s="4">
+        <v>103194</v>
+      </c>
+      <c r="D1403" s="2">
+        <v>46233.558287037027</v>
+      </c>
+      <c r="E1403" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1403" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1403" s="4" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H1403" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1403" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1403" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1403" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1404" s="4">
+        <v>408</v>
+      </c>
+      <c r="B1404" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1404" s="4">
+        <v>106622</v>
+      </c>
+      <c r="D1404" s="2">
+        <v>46233.631863425922</v>
+      </c>
+      <c r="E1404" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1404" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1404" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="H1404" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1404" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1404" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1404" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1405" s="4">
+        <v>409</v>
+      </c>
+      <c r="B1405" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1405" s="4">
+        <v>95559</v>
+      </c>
+      <c r="D1405" s="2">
+        <v>46233.677673611113</v>
+      </c>
+      <c r="E1405" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1405" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1405" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="H1405" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1405" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1405" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1405" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1406" s="4">
+        <v>410</v>
+      </c>
+      <c r="B1406" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1406" s="4">
+        <v>98178</v>
+      </c>
+      <c r="D1406" s="2">
+        <v>46233.796076388891</v>
+      </c>
+      <c r="E1406" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1406" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1406" s="4" t="s">
+        <v>1574</v>
+      </c>
+      <c r="H1406" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1406" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1406" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1406" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1407" s="4">
+        <v>411</v>
+      </c>
+      <c r="B1407" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1407" s="4">
+        <v>106837</v>
+      </c>
+      <c r="D1407" s="2">
+        <v>46234.202592592592</v>
+      </c>
+      <c r="E1407" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1407" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1407" s="4" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H1407" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="I1407" s="4" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J1407" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1407" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1408" s="4">
+        <v>412</v>
+      </c>
+      <c r="C1408" s="4">
+        <v>92325</v>
+      </c>
+      <c r="D1408" s="2">
+        <v>46234.59043152778</v>
+      </c>
+      <c r="E1408" s="4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F1408" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1408" s="4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="H1408" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1408" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1408" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1408" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+      <c r="A1409" s="4">
+        <v>413</v>
+      </c>
+      <c r="B1409" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1409" s="4">
+        <v>108099</v>
+      </c>
+      <c r="D1409" s="2">
+        <v>46234.605979837965</v>
+      </c>
+      <c r="E1409" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="F1409" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1409" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="H1409" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1409" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="J1409" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1409" s="4" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1410" s="4">
+        <v>414</v>
+      </c>
+      <c r="B1410" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1410" s="4">
+        <v>87586</v>
+      </c>
+      <c r="D1410" s="2">
+        <v>46234.643638819442</v>
+      </c>
+      <c r="E1410" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1410" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1410" s="4" t="s">
+        <v>1579</v>
+      </c>
+      <c r="H1410" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1410" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1410" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1410" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1411" s="4">
+        <v>415</v>
+      </c>
+      <c r="B1411" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1411" s="4">
+        <v>99308</v>
+      </c>
+      <c r="D1411" s="2">
+        <v>46234.773582997688</v>
+      </c>
+      <c r="E1411" s="4" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F1411" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1411" s="4" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H1411" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1411" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1411" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1411" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1412" s="4">
+        <v>416</v>
+      </c>
+      <c r="B1412" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1412" s="4">
+        <v>103189</v>
+      </c>
+      <c r="D1412" s="2">
+        <v>46234.832082858797</v>
+      </c>
+      <c r="E1412" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1412" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1412" s="4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="H1412" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1412" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1412" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1412" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1413" s="4">
+        <v>417</v>
+      </c>
+      <c r="B1413" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1413" s="4">
+        <v>103176</v>
+      </c>
+      <c r="D1413" s="2">
+        <v>46234.918748553238</v>
+      </c>
+      <c r="E1413" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1413" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1413" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H1413" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1413" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1413" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1413" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1414" s="4">
+        <v>418</v>
+      </c>
+      <c r="B1414" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1414" s="4">
+        <v>90447</v>
+      </c>
+      <c r="D1414" s="2">
+        <v>46236.780051770831</v>
+      </c>
+      <c r="E1414" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F1414" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1414" s="4" t="s">
+        <v>1585</v>
+      </c>
+      <c r="H1414" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1414" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1414" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1414" s="4" t="s">
         <v>1441</v>
       </c>
     </row>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/NPS Franquias/nps-franquias/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="383" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9F7506C-0E86-4557-BACF-E1FFEFB99F88}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09789F30-026A-4D33-8660-E3A83D510FDD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11314" uniqueCount="1586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11456" uniqueCount="1618">
   <si>
     <t>ID</t>
   </si>
@@ -4953,12 +4953,113 @@
   <si>
     <t>O técnico foi fazer a manutenção semestral e deixou o filtro com um barulho ensurdecedor.</t>
   </si>
+  <si>
+    <t>SEMPRE DIFICULDADES DE TROCA DO FILTRO A CADA 6 MESES VCS SÓ TROCAM A CADA ANO E NÃO CONCORDAMOS. NESSA ÚLTIMA VEZ NÃO RECEBI AVISO DA VISITA DA MANUNTENÇÃO E TIVERAM MUITA SORTE QUE HAVIA GENTE NO APARTAMENTO.E FIZERAM A MANUTENÇÃO SEM A PRESENÇA DO RESPONSÁVEL.</t>
+  </si>
+  <si>
+    <t>Esse serviço de atendimento de máquina é horrível, a máquina está programada para o benefício da BRASTEMP, não existe outro canal além de pessoas ligarem em nome da brastemp para cobrança. Serviço anti profissional, sem transparência e irritante. Marcam visitas e o técnico não aparece, você se indispoe com esse serviço confuso e nada prático. Está pior do que antes, penso até de encerrar o contrato.</t>
+  </si>
+  <si>
+    <t>Meu purificador continua com o gotejamento do qual eu havia reclamado, o técnico não fez nada para consertar...</t>
+  </si>
+  <si>
+    <t>PÉSSIMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não tem atendimento, mais fácil falar com o papa do que falar com vocês </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pela primeira vez vocês chegaram dentro da hora marcada.
+   Porém quando entrei em contato pedi um concerto, falei o que estava acontecendo e a empresa esqueceu de me falar que eu teria que desligar da tomada com 24 hs de antecedência, final nao puderam fazer o serviço. 
+   É lamentável </t>
+  </si>
+  <si>
+    <t>Na sexta dia 31, o tecnico veio para constar o defeito no aparelho e marcamos para terça dia 4/08 MANHA para a troca da peça, hoje recebi a mensagem para confirmar para dia 4/08 tarde. Não foi o combinado e depois de passar um tempao no telefone para conseguir um atendimento não virtual, a atendente não fez nenhum esforço para eu poder reestabelecer o meu agendamento que fizemos na sexta com o tecnico ou seja dia 4/08 MANHA. A unica solução foi aceitar o agendamento TARDE senão, o conserto ia para outra semana. Estou sem agua gelada já faz muito tempo e acho absurdo essa dificuldade para consertar. Pensando em trocar de fornecedor. O atendimento da Brastemp é péssimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicitei a instalação de um pressurizador, assim que o técnico foi embora o meu bebedor começou a vazar água, já vieram dois técnicos e o problema não foi resolvido, já estou agendando mais uma visita. Esse é o meu problema com a Culligan no momento.
+</t>
+  </si>
+  <si>
+    <t>Entrei para solicitar a troca de titularidade e fui informada que levará 45 dias para formalizar. Solicitei então a fatura, pois o débito automático foi descadastrado sem motivo e sem aviso, informaram que não tinham acesso e que terei que ligar novamente no dia do vencimento para solicitar. 40 minutos para isso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desisti do serviço. Muitos chamados não atendidos, queixas repetidas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Tecnico não apareceu como sempre
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A pessoa que veio aqui não deixou documento com data de revisão, e não trocou o filtro. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipamento mal instalado. Ficou vazando água. Não funciona corretamente na função gaseificada. Péssimo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">porque deixou o filtro com botao ruim
+</t>
+  </si>
+  <si>
+    <t>Motivo</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>"péssimo" sem motivo específico</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>impossível contato, sem atendimento</t>
+  </si>
+  <si>
+    <t>esqueceram de avisar desligar tomada 24h</t>
+  </si>
+  <si>
+    <t>agendamento alterado + atendente não ajudou + sem água gelada</t>
+  </si>
+  <si>
+    <t>REVISAR</t>
+  </si>
+  <si>
+    <t>bebedouro vazou após visita + reincidência (R5)</t>
+  </si>
+  <si>
+    <t>troca filtro 6/6 meses não feita + sem aviso (R10)</t>
+  </si>
+  <si>
+    <t>atendimento não resolve, 40 min</t>
+  </si>
+  <si>
+    <t>chamados não atendidos, queixas repetidas (R10)</t>
+  </si>
+  <si>
+    <t>técnico não apareceu (R8)</t>
+  </si>
+  <si>
+    <t>sem comprovante + não trocou filtro (R3)</t>
+  </si>
+  <si>
+    <t>atendimento robotizado ruim + técnico não aparece</t>
+  </si>
+  <si>
+    <t>mal instalado, vazando + não gaseifica (R5)</t>
+  </si>
+  <si>
+    <t>filtro com botão ruim após serviço</t>
+  </si>
+  <si>
+    <t>gotejamento persiste, técnico não consertou (R10)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4972,16 +5073,29 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -5004,11 +5118,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5024,6 +5149,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5325,9 +5456,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="8">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A99F678C-0A58-4B38-BD6D-52FA45E08A1C}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;779238cc-993e-4694-81ed-dd28055a6f94&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1414"/>
+  <dimension ref="A1:M1428"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -5344,7 +5497,7 @@
     <col min="12" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5378,8 +5531,14 @@
       <c r="K1" s="4" t="s">
         <v>1438</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5414,7 +5573,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5449,7 +5608,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5484,7 +5643,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5519,7 +5678,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5554,7 +5713,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5589,7 +5748,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5624,7 +5783,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5659,7 +5818,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5694,7 +5853,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5729,7 +5888,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5764,7 +5923,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5799,7 +5958,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5834,7 +5993,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5869,7 +6028,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -54621,7 +54780,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1409" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A1409" s="4">
         <v>413</v>
       </c>
@@ -54656,7 +54815,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="1410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1410" s="4">
         <v>414</v>
       </c>
@@ -54691,7 +54850,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1411" s="4">
         <v>415</v>
       </c>
@@ -54726,7 +54885,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1412" s="4">
         <v>416</v>
       </c>
@@ -54761,7 +54920,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1413" s="4">
         <v>417</v>
       </c>
@@ -54796,7 +54955,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1414" s="4">
         <v>418</v>
       </c>
@@ -54831,7 +54990,582 @@
         <v>1441</v>
       </c>
     </row>
+    <row r="1415" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1415" s="4">
+        <v>419</v>
+      </c>
+      <c r="B1415" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1415" s="4">
+        <v>93363</v>
+      </c>
+      <c r="D1415" s="2">
+        <v>46237.667943263892</v>
+      </c>
+      <c r="E1415" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1415" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1415" s="4" t="s">
+        <v>1589</v>
+      </c>
+      <c r="H1415" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1415" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1415" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1415" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1415" s="4" t="s">
+        <v>1602</v>
+      </c>
+      <c r="M1415" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1416" s="4">
+        <v>420</v>
+      </c>
+      <c r="B1416" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1416" s="4">
+        <v>108557</v>
+      </c>
+      <c r="D1416" s="2">
+        <v>46237.680220752314</v>
+      </c>
+      <c r="E1416" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F1416" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1416" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H1416" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1416" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1416" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1416" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1416" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="M1416" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1417" s="4">
+        <v>421</v>
+      </c>
+      <c r="B1417" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1417" s="4">
+        <v>105311</v>
+      </c>
+      <c r="D1417" s="2">
+        <v>46237.693124479163</v>
+      </c>
+      <c r="E1417" s="6" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1417" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1417" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="H1417" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1417" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1417" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1417" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1417" s="4" t="s">
+        <v>1605</v>
+      </c>
+      <c r="M1417" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1418" s="4">
+        <v>422</v>
+      </c>
+      <c r="B1418" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1418" s="4">
+        <v>104155</v>
+      </c>
+      <c r="D1418" s="2">
+        <v>46237.922759918984</v>
+      </c>
+      <c r="E1418" s="7" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1418" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1418" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H1418" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1418" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1418" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1418" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1418" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="M1418" s="4" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1419" s="4">
+        <v>423</v>
+      </c>
+      <c r="B1419" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1419" s="4">
+        <v>112676</v>
+      </c>
+      <c r="D1419" s="2">
+        <v>46237.985251817132</v>
+      </c>
+      <c r="E1419" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1419" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1419" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="H1419" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1419" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1419" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1419" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1419" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="M1419" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1420" s="4">
+        <v>424</v>
+      </c>
+      <c r="B1420" s="7" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1420" s="4">
+        <v>98227</v>
+      </c>
+      <c r="D1420" s="2">
+        <v>46237.994408136576</v>
+      </c>
+      <c r="E1420" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F1420" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1420" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="H1420" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1420" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1420" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1420" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1420" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M1420" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1421" s="4">
+        <v>425</v>
+      </c>
+      <c r="B1421" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1421" s="4">
+        <v>105177</v>
+      </c>
+      <c r="D1421" s="2">
+        <v>46238.55375561343</v>
+      </c>
+      <c r="E1421" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1421" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1421" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="H1421" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="I1421" s="4" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J1421" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1421" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1421" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="M1421" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1422" s="4">
+        <v>426</v>
+      </c>
+      <c r="B1422" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1422" s="4">
+        <v>101549</v>
+      </c>
+      <c r="D1422" s="2">
+        <v>46238.658281145836</v>
+      </c>
+      <c r="E1422" s="7" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1422" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1422" s="4" t="s">
+        <v>1595</v>
+      </c>
+      <c r="H1422" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1422" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1422" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1422" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1422" s="4" t="s">
+        <v>1611</v>
+      </c>
+      <c r="M1422" s="4" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1423" s="4">
+        <v>427</v>
+      </c>
+      <c r="B1423" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1423" s="4">
+        <v>95266</v>
+      </c>
+      <c r="D1423" s="2">
+        <v>46238.74402096065</v>
+      </c>
+      <c r="E1423" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1423" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1423" s="4" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H1423" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1423" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1423" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1423" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1423" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="M1423" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1424" s="4">
+        <v>428</v>
+      </c>
+      <c r="B1424" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1424" s="4">
+        <v>95186</v>
+      </c>
+      <c r="D1424" s="2">
+        <v>46238.750557662039</v>
+      </c>
+      <c r="E1424" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1424" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1424" s="4" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H1424" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1424" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1424" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1424" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1424" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="M1424" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1425" s="4">
+        <v>429</v>
+      </c>
+      <c r="B1425" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1425" s="4">
+        <v>104439</v>
+      </c>
+      <c r="D1425" s="2">
+        <v>46239.074787708334</v>
+      </c>
+      <c r="E1425" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1425" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1425" s="4" t="s">
+        <v>1587</v>
+      </c>
+      <c r="H1425" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1425" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1425" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1425" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1425" s="4" t="s">
+        <v>1614</v>
+      </c>
+      <c r="M1425" s="4" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1426" s="4">
+        <v>430</v>
+      </c>
+      <c r="B1426" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1426" s="4">
+        <v>88461</v>
+      </c>
+      <c r="D1426" s="2">
+        <v>46239.552590254629</v>
+      </c>
+      <c r="E1426" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1426" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1426" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="H1426" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1426" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1426" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1426" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1426" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="M1426" s="4" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1427" s="4">
+        <v>431</v>
+      </c>
+      <c r="B1427" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1427" s="4">
+        <v>103851</v>
+      </c>
+      <c r="D1427" s="2">
+        <v>46239.637758738427</v>
+      </c>
+      <c r="E1427" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1427" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1427" s="4" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H1427" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1427" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1427" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1427" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="L1427" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="M1427" s="4" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1428" s="4">
+        <v>432</v>
+      </c>
+      <c r="B1428" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1428" s="4">
+        <v>109246</v>
+      </c>
+      <c r="D1428" s="2">
+        <v>46239.658815532406</v>
+      </c>
+      <c r="E1428" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1428" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1428" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H1428" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1428" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1428" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1428" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1428" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="M1428" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09789F30-026A-4D33-8660-E3A83D510FDD}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1B5784-40C2-4465-AEE7-3CA41A033BC2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11456" uniqueCount="1618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11434" uniqueCount="1601">
   <si>
     <t>ID</t>
   </si>
@@ -5001,58 +5001,7 @@
 </t>
   </si>
   <si>
-    <t>Motivo</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>"péssimo" sem motivo específico</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>impossível contato, sem atendimento</t>
-  </si>
-  <si>
-    <t>esqueceram de avisar desligar tomada 24h</t>
-  </si>
-  <si>
-    <t>agendamento alterado + atendente não ajudou + sem água gelada</t>
-  </si>
-  <si>
-    <t>REVISAR</t>
-  </si>
-  <si>
-    <t>bebedouro vazou após visita + reincidência (R5)</t>
-  </si>
-  <si>
-    <t>troca filtro 6/6 meses não feita + sem aviso (R10)</t>
-  </si>
-  <si>
-    <t>atendimento não resolve, 40 min</t>
-  </si>
-  <si>
-    <t>chamados não atendidos, queixas repetidas (R10)</t>
-  </si>
-  <si>
-    <t>técnico não apareceu (R8)</t>
-  </si>
-  <si>
-    <t>sem comprovante + não trocou filtro (R3)</t>
-  </si>
-  <si>
-    <t>atendimento robotizado ruim + técnico não aparece</t>
-  </si>
-  <si>
-    <t>mal instalado, vazando + não gaseifica (R5)</t>
-  </si>
-  <si>
-    <t>filtro com botão ruim após serviço</t>
-  </si>
-  <si>
-    <t>gotejamento persiste, técnico não consertou (R10)</t>
+    <t xml:space="preserve">Pq a Culligan me passou informaçoes indevidas ref, numero do caso e numero OS, por várias vezes que o técnico veio para fazer o servico, e nao batia as informaçoes. Inclusive no dia 04/08/26 o técnico só subiu, pq o zelador o acompanhou e ficou junto enqto ele fazia o serviço, e eu fiquei fora do apto rezando p/ que nao fosse um ladrao! ISSO É UM ABSURDO!!!! </t>
   </si>
 </sst>
 </file>
@@ -5480,7 +5429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1428"/>
+  <dimension ref="A1:K1429"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -5497,7 +5446,7 @@
     <col min="12" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5531,14 +5480,8 @@
       <c r="K1" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>1600</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5573,7 +5516,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5608,7 +5551,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5643,7 +5586,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5678,7 +5621,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5713,7 +5656,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5748,7 +5691,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5783,7 +5726,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5818,7 +5761,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5853,7 +5796,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5888,7 +5831,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5923,7 +5866,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5958,7 +5901,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5993,7 +5936,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -6028,7 +5971,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -54780,7 +54723,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1409" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="1409" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A1409" s="4">
         <v>413</v>
       </c>
@@ -54815,7 +54758,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="1410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1410" s="4">
         <v>414</v>
       </c>
@@ -54850,7 +54793,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1411" s="4">
         <v>415</v>
       </c>
@@ -54885,7 +54828,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1412" s="4">
         <v>416</v>
       </c>
@@ -54920,7 +54863,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1413" s="4">
         <v>417</v>
       </c>
@@ -54955,7 +54898,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1414" s="4">
         <v>418</v>
       </c>
@@ -54990,7 +54933,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="1415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1415" s="4">
         <v>419</v>
       </c>
@@ -55024,14 +54967,8 @@
       <c r="K1415" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1415" s="4" t="s">
-        <v>1602</v>
-      </c>
-      <c r="M1415" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1416" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1416" s="4">
         <v>420</v>
       </c>
@@ -55065,14 +55002,8 @@
       <c r="K1416" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1416" s="4" t="s">
-        <v>1604</v>
-      </c>
-      <c r="M1416" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1417" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1417" s="4">
         <v>421</v>
       </c>
@@ -55106,14 +55037,8 @@
       <c r="K1417" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1417" s="4" t="s">
-        <v>1605</v>
-      </c>
-      <c r="M1417" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1418" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1418" s="4">
         <v>422</v>
       </c>
@@ -55147,14 +55072,8 @@
       <c r="K1418" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1418" s="4" t="s">
-        <v>1606</v>
-      </c>
-      <c r="M1418" s="4" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="1419" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1419" s="4">
         <v>423</v>
       </c>
@@ -55188,14 +55107,8 @@
       <c r="K1419" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1419" s="4" t="s">
-        <v>1608</v>
-      </c>
-      <c r="M1419" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1420" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1420" s="4">
         <v>424</v>
       </c>
@@ -55229,14 +55142,8 @@
       <c r="K1420" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1420" s="4" t="s">
-        <v>1609</v>
-      </c>
-      <c r="M1420" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1421" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1421" s="4">
         <v>425</v>
       </c>
@@ -55270,14 +55177,8 @@
       <c r="K1421" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1421" s="4" t="s">
-        <v>1610</v>
-      </c>
-      <c r="M1421" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1422" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1422" s="4">
         <v>426</v>
       </c>
@@ -55311,14 +55212,8 @@
       <c r="K1422" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1422" s="4" t="s">
-        <v>1611</v>
-      </c>
-      <c r="M1422" s="4" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="1423" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1423" s="4">
         <v>427</v>
       </c>
@@ -55352,14 +55247,8 @@
       <c r="K1423" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1423" s="4" t="s">
-        <v>1612</v>
-      </c>
-      <c r="M1423" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1424" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1424" s="4">
         <v>428</v>
       </c>
@@ -55393,14 +55282,8 @@
       <c r="K1424" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1424" s="4" t="s">
-        <v>1613</v>
-      </c>
-      <c r="M1424" s="4" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="1425" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1425" s="4">
         <v>429</v>
       </c>
@@ -55434,14 +55317,8 @@
       <c r="K1425" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1425" s="4" t="s">
-        <v>1614</v>
-      </c>
-      <c r="M1425" s="4" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="1426" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1426" s="4">
         <v>430</v>
       </c>
@@ -55475,14 +55352,8 @@
       <c r="K1426" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1426" s="4" t="s">
-        <v>1615</v>
-      </c>
-      <c r="M1426" s="4" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="1427" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1427" s="4">
         <v>431</v>
       </c>
@@ -55516,14 +55387,8 @@
       <c r="K1427" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="L1427" s="4" t="s">
-        <v>1616</v>
-      </c>
-      <c r="M1427" s="4" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="1428" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1428" s="4">
         <v>432</v>
       </c>
@@ -55557,11 +55422,40 @@
       <c r="K1428" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="L1428" s="4" t="s">
-        <v>1617</v>
-      </c>
-      <c r="M1428" s="4" t="s">
-        <v>1603</v>
+    </row>
+    <row r="1429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1429" s="4">
+        <v>433</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1429">
+        <v>104833</v>
+      </c>
+      <c r="D1429" s="2">
+        <v>46239.658815532406</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>1600</v>
+      </c>
+      <c r="H1429" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1429" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1429" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1429" s="4" t="s">
+        <v>1440</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1B5784-40C2-4465-AEE7-3CA41A033BC2}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E3DBA3-F6BA-4ADD-9D72-7EB751D62698}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2580" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11434" uniqueCount="1601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11498" uniqueCount="1610">
   <si>
     <t>ID</t>
   </si>
@@ -5002,6 +5002,42 @@
   </si>
   <si>
     <t xml:space="preserve">Pq a Culligan me passou informaçoes indevidas ref, numero do caso e numero OS, por várias vezes que o técnico veio para fazer o servico, e nao batia as informaçoes. Inclusive no dia 04/08/26 o técnico só subiu, pq o zelador o acompanhou e ficou junto enqto ele fazia o serviço, e eu fiquei fora do apto rezando p/ que nao fosse um ladrao! ISSO É UM ABSURDO!!!! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havia agendado entre 08:00 e 13:00… fiquei esperando até 13:12 
+Cancelei porque tinha que sair….. 
+para minha supresa quando voltei para casa às 14:00 soube que o técnico veio e quem teve de atender foi minha esposa que estava acamada…..vergonha f de o atendimento, que piorou muito depois da união Brastemp-Culligan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embora instalação tenha sido realizada.
+O grande problema ocorreu entre a equipe de agendamento e instalação, aguardamos 2 sábados, dia permitido para instalação e mesmo com a confirmação de agendamento, o técnico não compareceu, por se tratar de dia que o escritório fecha, causou mais transtorno. Tivemos que convocar um funcionário somente para receber o técnico e ficou aguardando todo o período de 8h00 as 13h00, tempo e dinheiro perdido.
+Durante a semana, ficavam tentando ir instalar, sem agendamento, mesmo sendo informado que não seria permitido. Bem Desorganizado.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque achei que o filtro seria trocado de 6 em 6 meses, pra ter valido a pena eu ter assinado o serviço.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico não atendeu o que precisava ser feito, e empresa demora muito para agendar uma simples troca de filtro que já tinha passado do prazo de troca </t>
+  </si>
+  <si>
+    <t>Tudo nessa empresa é demorado. Vou cancelar o meu contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prestador serviço  de  nome  Caique  Ribeiro não  fez  teste  na  água, preciso trocar meu aparelho  desde que assinei o contrato está com problemas no botão da saída de água. 
+já foi  feito  diversos  reparos  em todas as manutenção  e  nunca  resolve,  e  simplesmente o técnico disse  que  era  mais  fácil eu  cancelar a  assinatura  porque  dava  muito  trabalho para  ele  fazer a  troca,  tinha  que  filmar  o  problema  em  fim,  para  eu  cancelar e  depois pedir  de  novo  acredita ,  para  não  ter  trabalho. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fiquei impressionado com a velocidade que o prestador de serviço, Erivan Luciano da Silva entrou e saiu condomínio, e ainda fez a manutenção, 15 minutos, e pedindo esclarecimentos através do telefone 11 98699-7958 sobre o procedimento de atendimento, a atendente Layane, pouco se interessou em ouvir minha reclamação, mandando eu aguardar o protocolo 00264921.
+Conforme for o laudo que eu receber, irei procurar maiores esclarecimentos através do Jurídico.
+</t>
+  </si>
+  <si>
+    <t>Horrível, muito tempo esperando a manutenção em um bebedouro com a agua amarela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo </t>
   </si>
 </sst>
 </file>
@@ -5082,7 +5118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5104,6 +5140,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5429,7 +5468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1429"/>
+  <dimension ref="A1:K1437"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -55458,6 +55497,286 @@
         <v>1440</v>
       </c>
     </row>
+    <row r="1430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1430" s="4">
+        <v>434</v>
+      </c>
+      <c r="B1430" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1430" s="8">
+        <v>103626</v>
+      </c>
+      <c r="D1430" s="2">
+        <v>46240.428025729168</v>
+      </c>
+      <c r="E1430" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1430" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1430" s="8" t="s">
+        <v>1601</v>
+      </c>
+      <c r="H1430" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1430" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1430" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1430" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1431" s="4">
+        <v>435</v>
+      </c>
+      <c r="B1431" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1431" s="8">
+        <v>110309</v>
+      </c>
+      <c r="D1431" s="2">
+        <v>46240.522614340283</v>
+      </c>
+      <c r="E1431" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1431" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1431" s="8" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H1431" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1431" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1431" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1431" s="8" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1432" s="4">
+        <v>436</v>
+      </c>
+      <c r="B1432" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1432" s="8">
+        <v>114401</v>
+      </c>
+      <c r="D1432" s="2">
+        <v>46240.554278495372</v>
+      </c>
+      <c r="E1432" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1432" s="8" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H1432" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1432" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1432" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1432" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1433" s="4">
+        <v>437</v>
+      </c>
+      <c r="B1433" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1433" s="8">
+        <v>112740</v>
+      </c>
+      <c r="D1433" s="2">
+        <v>46240.566327060187</v>
+      </c>
+      <c r="E1433" s="8" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1433" s="8" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H1433" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1433" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1433" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1433" s="8" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1434" s="4">
+        <v>438</v>
+      </c>
+      <c r="B1434" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1434" s="8">
+        <v>98452</v>
+      </c>
+      <c r="D1434" s="2">
+        <v>46240.703195682872</v>
+      </c>
+      <c r="E1434" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F1434" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1434" s="8" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H1434" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="I1434" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1434" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1434" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1435" s="4">
+        <v>439</v>
+      </c>
+      <c r="B1435" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1435" s="8">
+        <v>110003</v>
+      </c>
+      <c r="D1435" s="2">
+        <v>46240.721779143518</v>
+      </c>
+      <c r="E1435" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1435" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1435" s="8" t="s">
+        <v>1606</v>
+      </c>
+      <c r="H1435" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1435" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1435" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1435" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1436" s="4">
+        <v>440</v>
+      </c>
+      <c r="B1436" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1436" s="8">
+        <v>89116</v>
+      </c>
+      <c r="D1436" s="2">
+        <v>46240.751161192129</v>
+      </c>
+      <c r="E1436" s="8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F1436" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1436" s="8" t="s">
+        <v>1607</v>
+      </c>
+      <c r="H1436" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1436" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1436" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1436" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1437" s="4">
+        <v>441</v>
+      </c>
+      <c r="B1437" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1437" s="8">
+        <v>113608</v>
+      </c>
+      <c r="D1437" s="2">
+        <v>46240.822670208327</v>
+      </c>
+      <c r="E1437" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1437" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1437" s="8" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H1437" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1437" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1437" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1437" s="8" t="s">
+        <v>1463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E3DBA3-F6BA-4ADD-9D72-7EB751D62698}"/>
+  <xr:revisionPtr revIDLastSave="616" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BEBF561-D19C-459A-89D6-5A7D18CDF1B6}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-2580" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="1920" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1414</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1450</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11498" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11630" uniqueCount="1644">
   <si>
     <t>ID</t>
   </si>
@@ -5039,12 +5039,128 @@
   <si>
     <t xml:space="preserve">Campo </t>
   </si>
+  <si>
+    <t>FRQ CAMPINAS R02</t>
+  </si>
+  <si>
+    <t>FRQ RECIFE PE R02</t>
+  </si>
+  <si>
+    <t>AT NATAL RN R01 - MATRIZ</t>
+  </si>
+  <si>
+    <t>FRQ SJCAMPOS SP R02 - MATRIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Não fez o que precisava. Chega sempre no horário de almoço que foi pedido para eu acompanhar , não faz o combinado nunca com o cliente. Insatisfeito. /// e esta demorando para instalar o outro equipamento que tenho .. isso porque sou cliente a muito tempo e tenho 05 purificadores.  </t>
+  </si>
+  <si>
+    <t>O aparelho foi consertado mas achei que diante da extrema necessidade demorar 4 dias para atender foi muito já que se trata de agua para beber. Mas o funcionário foi excelente e consertou o defeito quando esteve aqui.</t>
+  </si>
+  <si>
+    <t>Minha insatisfação com empresa Brastemp e Culligan é gigante!
+Se eu fosse citar todos os.problemas que eu estou tendo esse espaço aqui tá pequeno.
+E de verdade essa pesquisa, não passe de uma mentira porque nem a reclamação que eu fiz no site RECLAME AQUI, a empresa se importou. 
+Vocês simplesmente ignora nossas reclamações, atendentes(humanos) despreparados, não te dão devolutiva de um protocolo quando dão , não sabe nem do que se trata.
+É uma falta de respeito e olha que eu tinha 3 FILTROS, estou CANCELANDO TODOS e com certeza meu marketing será NEGATIVO.</t>
+  </si>
+  <si>
+    <t>DE ACORDO COM MINHA SOLICITAÇÃO VEIO UM TÉCNICO NO ÚLTIMO DIA 06 DE AGOSTO. NÃO TERMINOU O SERVIÇO E FICOU , EM PRINCÍPIO, QUE SERIA CONCLUÍDO O REPARO EM 48 HS. NO DIA 08 FIQUEI ESPERANDO A VINDA DE UM TÉCNICO. COMO ESTAVA FICANDO TARDE, LIGUEI PARA A BRASTEMP E FUI INFORMADO DE QUE HAVIA UM AGENDAMENTO PARA VISITA TÉCNICA PARA O DIA 25. CONSEGUI COM A ATENDENTE MUDAR PARA O PRÓXIMO DIA 11. ESPERA QUE O SERVIÇO SEJA CONCLUÍDO, ENTÃO.</t>
+  </si>
+  <si>
+    <t>Pois marcamos a troca de dois elementos filtrantes, pois temos 02 contratos e a troca do botão de um deles de liga e desliga. O funcionário foi excelente ,mas fiz a marcação por telefone e sempre agendam errado.
+Estou no aguardo para a troca do elemento filtrante e do botão de liga e desliga. Urgente</t>
+  </si>
+  <si>
+    <t>Agendaram uma visita técnica para troca do filtro do purificador e NÃO CUMPRIRAM, remarcando para mais de uma semana, apesar dos meus argumentos de que estávamos sem usar o purificador.</t>
+  </si>
+  <si>
+    <t>Boa tarde.
+Já solicitei diversas vezes o conserto do seletor de nível automático e minha solicitação foi simplesmente ignorada. Gostaria de reclamar e solicitar mais uma vez o reparo do seletor de nível automático.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Purificador não está funcionando! 
+Acionei assistência o mesmo condenou o Purificador! 
+Estou aguardando a substituição! 
+Até o momento não houve nenhum retorno para que seja substituído! </t>
+  </si>
+  <si>
+    <t>O tempo de agendamento para atendimento é muito longo.
+Abri o chamado e só fui atendido 2 semanas depois.
+O elemento filtrante estava muito sujoe e quase não saía mais água do equipamento.
+Muito decepcionado.</t>
+  </si>
+  <si>
+    <t>Demora em substituir o purificador depois da solicitação e, quando substituído, o novo não gelava. No mesmo dia foi solicitado o reparo, faz quase 20 dias que estamos com o equipamento novo sem gelar. O principal motivo de ter um equipamento locado é de ter sua troca o reparo em tempo reduzido. Sem essa vantagem não faz sentido ter este equipamento alugado.</t>
+  </si>
+  <si>
+    <t>Melhorar no cumprimento das realizações das visitas técnicas agendadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Po e muito  difícil  marcar  um horário  para a manutenção,  pelo WhatsApp,  manca consigo  finaliza conversa 
+Fico falando  com um robô, quero falar com uma pessoa,  se for  falar  com um robô,  que seja bem programado por favor. </t>
+  </si>
+  <si>
+    <t>Filtro com problema é simplesmente só podem vir dia 18.
+Resultado: 10 dias sem filtro</t>
+  </si>
+  <si>
+    <t>Motivo (texto-chave detectado)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>chega sempre no horário de almoço, não faz o combinado + serviço não feito</t>
+  </si>
+  <si>
+    <t>REVISAR</t>
+  </si>
+  <si>
+    <t>demorou 4 dias para atender</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>atendentes despreparados, sem devolutiva de protocolo</t>
+  </si>
+  <si>
+    <t>não terminou o serviço + agenda distante (dia 25)</t>
+  </si>
+  <si>
+    <t>sempre agendam errado por telefone + troca pendente</t>
+  </si>
+  <si>
+    <t>agendaram visita e não cumpriram, remarcaram</t>
+  </si>
+  <si>
+    <t>solicitei diversas vezes, solicitação ignorada</t>
+  </si>
+  <si>
+    <t>aguardando substituição, nenhum retorno</t>
+  </si>
+  <si>
+    <t>atendido 2 semanas depois + quase não saía água</t>
+  </si>
+  <si>
+    <t>equipamento novo sem gelar há 20 dias + demora na troca</t>
+  </si>
+  <si>
+    <t>cumprimento das visitas técnicas agendadas</t>
+  </si>
+  <si>
+    <t>robô no WhatsApp, não consegue finalizar conversa</t>
+  </si>
+  <si>
+    <t>só podem vir dia 18, 10 dias sem filtro</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5059,6 +5175,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5118,7 +5242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5143,6 +5267,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5468,7 +5595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1437"/>
+  <dimension ref="A1:M1450"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -5482,10 +5609,12 @@
     <col min="9" max="9" width="28" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5703125" style="4" customWidth="1"/>
     <col min="11" max="11" width="18.140625" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="4"/>
+    <col min="12" max="12" width="30" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5519,8 +5648,14 @@
       <c r="K1" s="4" t="s">
         <v>1438</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="9" t="s">
+        <v>1627</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5555,7 +5690,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5590,7 +5725,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5625,7 +5760,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5660,7 +5795,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5695,7 +5830,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5730,7 +5865,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5765,7 +5900,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5800,7 +5935,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5835,7 +5970,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5870,7 +6005,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5905,7 +6040,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5940,7 +6075,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5975,7 +6110,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -6010,7 +6145,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -55322,7 +55457,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1425" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1425" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1425" s="4">
         <v>429</v>
       </c>
@@ -55357,7 +55492,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1426" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1426" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1426" s="4">
         <v>430</v>
       </c>
@@ -55392,7 +55527,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1427" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1427" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1427" s="4">
         <v>431</v>
       </c>
@@ -55427,7 +55562,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="1428" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1428" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1428" s="4">
         <v>432</v>
       </c>
@@ -55462,7 +55597,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1429" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1429" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1429" s="4">
         <v>433</v>
       </c>
@@ -55497,7 +55632,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1430" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1430" s="4">
         <v>434</v>
       </c>
@@ -55532,7 +55667,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1431" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1431" s="4">
         <v>435</v>
       </c>
@@ -55567,7 +55702,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="1432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1432" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1432" s="4">
         <v>436</v>
       </c>
@@ -55602,7 +55737,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1433" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1433" s="4">
         <v>437</v>
       </c>
@@ -55637,7 +55772,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="1434" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1434" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1434" s="4">
         <v>438</v>
       </c>
@@ -55672,7 +55807,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1435" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1435" s="4">
         <v>439</v>
       </c>
@@ -55707,7 +55842,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1436" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1436" s="4">
         <v>440</v>
       </c>
@@ -55742,7 +55877,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1437" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1437" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1437" s="4">
         <v>441</v>
       </c>
@@ -55775,6 +55910,539 @@
       </c>
       <c r="K1437" s="8" t="s">
         <v>1463</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1438" s="4">
+        <v>442</v>
+      </c>
+      <c r="B1438" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1438" s="8">
+        <v>99697</v>
+      </c>
+      <c r="D1438" s="2">
+        <v>46241.620372048608</v>
+      </c>
+      <c r="E1438" s="8" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1438" s="8" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H1438" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1438" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1438" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1438" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1438" s="4" t="s">
+        <v>1629</v>
+      </c>
+      <c r="M1438" s="4" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1439" s="4">
+        <v>443</v>
+      </c>
+      <c r="B1439" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1439" s="8">
+        <v>113396</v>
+      </c>
+      <c r="D1439" s="2">
+        <v>46241.794543969911</v>
+      </c>
+      <c r="E1439" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1439" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1439" s="8" t="s">
+        <v>1615</v>
+      </c>
+      <c r="H1439" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1439" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1439" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1439" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1439" s="4" t="s">
+        <v>1631</v>
+      </c>
+      <c r="M1439" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1440" s="4">
+        <v>444</v>
+      </c>
+      <c r="B1440" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1440" s="8">
+        <v>108029</v>
+      </c>
+      <c r="D1440" s="2">
+        <v>46243.6670446875</v>
+      </c>
+      <c r="E1440" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1440" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1440" s="8" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H1440" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1440" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1440" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1440" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1440" s="4" t="s">
+        <v>1633</v>
+      </c>
+      <c r="M1440" s="4" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1441" s="4">
+        <v>445</v>
+      </c>
+      <c r="B1441" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1441" s="8">
+        <v>116676</v>
+      </c>
+      <c r="D1441" s="2">
+        <v>46244.606537280088</v>
+      </c>
+      <c r="E1441" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F1441" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1441" s="8" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H1441" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1441" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1441" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1441" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1441" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="M1441" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1442" s="4">
+        <v>447</v>
+      </c>
+      <c r="B1442" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1442" s="8">
+        <v>105481</v>
+      </c>
+      <c r="D1442" s="2">
+        <v>46244.637655451392</v>
+      </c>
+      <c r="E1442" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1442" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1442" s="8" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1442" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1442" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1442" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1442" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1442" s="4" t="s">
+        <v>1635</v>
+      </c>
+      <c r="M1442" s="4" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1443" s="4">
+        <v>449</v>
+      </c>
+      <c r="B1443" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1443" s="8">
+        <v>114242</v>
+      </c>
+      <c r="D1443" s="2">
+        <v>46244.653732372688</v>
+      </c>
+      <c r="E1443" s="8" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1443" s="8" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H1443" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1443" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1443" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1443" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1443" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="M1443" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1444" s="4">
+        <v>450</v>
+      </c>
+      <c r="B1444" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1444" s="8">
+        <v>114262</v>
+      </c>
+      <c r="D1444" s="2">
+        <v>46244.674947638887</v>
+      </c>
+      <c r="E1444" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1444" s="8" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H1444" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1444" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1444" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1444" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1444" s="4" t="s">
+        <v>1637</v>
+      </c>
+      <c r="M1444" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1445" s="4">
+        <v>452</v>
+      </c>
+      <c r="B1445" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1445" s="8">
+        <v>115579</v>
+      </c>
+      <c r="D1445" s="2">
+        <v>46244.700219062499</v>
+      </c>
+      <c r="E1445" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1445" s="8" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H1445" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1445" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1445" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1445" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1445" s="4" t="s">
+        <v>1638</v>
+      </c>
+      <c r="M1445" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1446" s="4">
+        <v>453</v>
+      </c>
+      <c r="B1446" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1446" s="8">
+        <v>108581</v>
+      </c>
+      <c r="D1446" s="2">
+        <v>46244.711498854173</v>
+      </c>
+      <c r="E1446" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1446" s="8" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H1446" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1446" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1446" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1446" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1446" s="4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="M1446" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1447" s="4">
+        <v>454</v>
+      </c>
+      <c r="B1447" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1447" s="8">
+        <v>106871</v>
+      </c>
+      <c r="D1447" s="2">
+        <v>46244.757379641203</v>
+      </c>
+      <c r="E1447" s="8" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1447" s="8" t="s">
+        <v>1623</v>
+      </c>
+      <c r="H1447" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1447" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1447" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1447" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1447" s="4" t="s">
+        <v>1640</v>
+      </c>
+      <c r="M1447" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1448" s="4">
+        <v>455</v>
+      </c>
+      <c r="B1448" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1448" s="8">
+        <v>113979</v>
+      </c>
+      <c r="D1448" s="2">
+        <v>46244.787126689807</v>
+      </c>
+      <c r="E1448" s="8" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1448" s="8" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H1448" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1448" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1448" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1448" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1448" s="4" t="s">
+        <v>1641</v>
+      </c>
+      <c r="M1448" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1449" s="4">
+        <v>456</v>
+      </c>
+      <c r="B1449" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1449" s="8">
+        <v>107921</v>
+      </c>
+      <c r="D1449" s="2">
+        <v>46245.386342928243</v>
+      </c>
+      <c r="E1449" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1449" s="8" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H1449" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1449" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1449" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1449" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1449" s="4" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M1449" s="4" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1450" s="4">
+        <v>457</v>
+      </c>
+      <c r="B1450" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1450" s="8">
+        <v>115894</v>
+      </c>
+      <c r="D1450" s="2">
+        <v>46245.535121446759</v>
+      </c>
+      <c r="E1450" s="8" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1450" s="8" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H1450" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1450" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1450" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1450" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1450" s="4" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M1450" s="4" t="s">
+        <v>1632</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="616" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BEBF561-D19C-459A-89D6-5A7D18CDF1B6}"/>
+  <xr:revisionPtr revIDLastSave="633" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E2BB1C8-DB9A-48AB-9DCD-28A63353E629}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="1920" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1451</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11630" uniqueCount="1644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11638" uniqueCount="1645">
   <si>
     <t>ID</t>
   </si>
@@ -5154,6 +5154,9 @@
   </si>
   <si>
     <t>só podem vir dia 18, 10 dias sem filtro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa Tarde ! Colaborar atencioso e educado. Porém, minha insatisfação e com o cilindro de gás, estamos a mais de um ano tentado comprar um cilindro para agua com gás e voces não tem o produto para vender . </t>
   </si>
 </sst>
 </file>
@@ -5595,7 +5598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1450"/>
+  <dimension ref="A1:M1451"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -56445,6 +56448,41 @@
         <v>1632</v>
       </c>
     </row>
+    <row r="1451" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1451" s="4">
+        <v>458</v>
+      </c>
+      <c r="B1451" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1451" s="8">
+        <v>109945</v>
+      </c>
+      <c r="D1451" s="2">
+        <v>46245.77177752315</v>
+      </c>
+      <c r="E1451" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1451" s="8" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H1451" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1451" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1451" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1451" s="8" t="s">
+        <v>1441</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="633" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E2BB1C8-DB9A-48AB-9DCD-28A63353E629}"/>
+  <xr:revisionPtr revIDLastSave="705" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{270A3ED1-7987-4D50-A7AC-16BA09B62C38}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11638" uniqueCount="1645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11738" uniqueCount="1651">
   <si>
     <t>ID</t>
   </si>
@@ -5111,52 +5111,75 @@
     <t>Status</t>
   </si>
   <si>
-    <t>chega sempre no horário de almoço, não faz o combinado + serviço não feito</t>
-  </si>
-  <si>
-    <t>REVISAR</t>
-  </si>
-  <si>
-    <t>demorou 4 dias para atender</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>atendentes despreparados, sem devolutiva de protocolo</t>
-  </si>
-  <si>
-    <t>não terminou o serviço + agenda distante (dia 25)</t>
-  </si>
-  <si>
-    <t>sempre agendam errado por telefone + troca pendente</t>
-  </si>
-  <si>
-    <t>agendaram visita e não cumpriram, remarcaram</t>
-  </si>
-  <si>
-    <t>solicitei diversas vezes, solicitação ignorada</t>
-  </si>
-  <si>
-    <t>aguardando substituição, nenhum retorno</t>
-  </si>
-  <si>
-    <t>atendido 2 semanas depois + quase não saía água</t>
-  </si>
-  <si>
-    <t>equipamento novo sem gelar há 20 dias + demora na troca</t>
-  </si>
-  <si>
-    <t>cumprimento das visitas técnicas agendadas</t>
-  </si>
-  <si>
-    <t>robô no WhatsApp, não consegue finalizar conversa</t>
-  </si>
-  <si>
-    <t>só podem vir dia 18, 10 dias sem filtro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Boa Tarde ! Colaborar atencioso e educado. Porém, minha insatisfação e com o cilindro de gás, estamos a mais de um ano tentado comprar um cilindro para agua com gás e voces não tem o produto para vender . </t>
+  </si>
+  <si>
+    <t>15/08/2026</t>
+  </si>
+  <si>
+    <t>14/08/2026</t>
+  </si>
+  <si>
+    <t>13/08/2026</t>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>FRQ GOIANIA  GO R01</t>
+  </si>
+  <si>
+    <t>FRQ LIMEIRA SP R04</t>
+  </si>
+  <si>
+    <t>FRQ CAMPINAS R04</t>
+  </si>
+  <si>
+    <t>Falat de compromisso com o horário agendado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não atendem , pedi o atendimento </t>
+  </si>
+  <si>
+    <t>Pq mesmo estando anotado na ordem de serviço, não veio o elemento filtrante NiB gel, o filtro que foi retirado a manutenção tinha sido feita pela metade e um mês depois já precisou de nova manutenção, pois a água estava podre, cheirando muito mal e dentro do aparelho estava cheio de baratas! Espero que esse novo aparelho, esteja sem contaminação , sem baratas ou ovos e que a Culligan verifique aonde são guardados os elementos filtrantes e que haja um cuidado e controle de qualidade melhor!</t>
+  </si>
+  <si>
+    <t>Vieram aqui quarta de manhã dia 12/08 detectaram o furo na mangueira e a prestadora de serviço falou que iriam voltar no mesmo dia a tarde ou até na quinta de manhã, e até agora não vieram resolver o vazamento</t>
+  </si>
+  <si>
+    <t>Porque agendei 2 vezes e não apareceu ninguém. É muita falta de respeito com o tempo do cliente.</t>
+  </si>
+  <si>
+    <t>Na minha opinião, este serviço só compensa  se trocar o filtro a cada 06 meses.
+Fazer uma analise da agua e dizer que esta boa e ficar com um filtro 1ano é tentar economizar</t>
+  </si>
+  <si>
+    <t>De todos os atendimentos de manutenção semestral diria que esse foi o pior e que menos avaliou a real necessidade de troca ou não de peças.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meu purificador continua com um gosto de metal e continua esquentando muito. nada foi resolvido, só trocaram o filtro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O prestador de serviço fez o serviço ok, porém deixou sujeira no local, plástico pelo chão, sendo que a lixeira está ao lado do local onde ele fez o serviço. Lamentável. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiquei muito preocupada pela visita, sem crachá de Identificação e sem uniforme.
+A ordem de Serviço não tem nenhuma identificação, sem logomarca, nem endereço ou telefone de contato, não consta o CNPJ da empresa. Após ler toda a Ordem de Serviço, consegui encontrar o nome Culligar, no formato pequeno em uma linha na esquerda da Ordem de Serviço.  Sem telefone para contato. Embora o Técnico tenha sido  muito educado, simpático, respondendo minhas perguntas, não foi o suficiente para me tranquilizar. O que me deixou tranquila foi ele mencionar outros técnicos  da Brastemp conhecido por mim. Friso que o problema não foi o rapaz, mas Ordem de Serviço,  sem dados suficientes, imprecisa, que não passa nenhuma segurança para os clientes.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou solicitando a quase um mês que me enviem a fatura SEM SENHA, não bate com o meu CPF..
+Até agora não fui atendido.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agendei no período da tarde, chegaram pela manhã no primeiro horario. Deixei subir. 
+Fizeram a manutenção, ok. Mas nao me avisaram que vazou agua embaixo do filtro, ele fica em suporte de madeira em um movél planejado, eleS deixaram cheio de agua embaixo e não avisaram. Só foi notado bem depois, isso estraga o movél. Era algo tão simples era só avisar que molhou, não precisava secar, mas não, fecharam o filtro e colocaram a peça de suporte e não falaram nada. NOTA 0 PARA OS DOIS PROFISSIONAIS QUE ESTIVERAM AQUI. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quase um mês minha purificador  de água não  está gelando,  desde então estou tentando  entrar em contato e não  consigo falar com ser humano,  só robô,  ainda aguardando outro purificador e tb desconto na minha conta que esta muito  caro e tb mal atendido. </t>
+  </si>
+  <si>
+    <t>Porque vocês estão muito desorganizados, enviam o técnico sem fazer uma programação antecipada, sem avisar, e todas as vezes, nesses ultimos meses, tem pego nós desprevenidos, isso demonstra uma total falta de organização e respeito com o cliente!</t>
   </si>
 </sst>
 </file>
@@ -5598,7 +5621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1451"/>
+  <dimension ref="A1:M1465"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -55460,7 +55483,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1425" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1425" s="4">
         <v>429</v>
       </c>
@@ -55495,7 +55518,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1426" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1426" s="4">
         <v>430</v>
       </c>
@@ -55530,7 +55553,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1427" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1427" s="4">
         <v>431</v>
       </c>
@@ -55565,7 +55588,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="1428" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1428" s="4">
         <v>432</v>
       </c>
@@ -55600,7 +55623,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1429" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1429" s="4">
         <v>433</v>
       </c>
@@ -55635,7 +55658,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1430" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1430" s="4">
         <v>434</v>
       </c>
@@ -55670,7 +55693,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1431" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1431" s="4">
         <v>435</v>
       </c>
@@ -55705,7 +55728,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="1432" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1432" s="4">
         <v>436</v>
       </c>
@@ -55740,7 +55763,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1433" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1433" s="4">
         <v>437</v>
       </c>
@@ -55775,7 +55798,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="1434" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1434" s="4">
         <v>438</v>
       </c>
@@ -55810,7 +55833,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1435" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1435" s="4">
         <v>439</v>
       </c>
@@ -55845,7 +55868,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1436" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1436" s="4">
         <v>440</v>
       </c>
@@ -55880,7 +55903,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1437" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1437" s="4">
         <v>441</v>
       </c>
@@ -55915,7 +55938,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="1438" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1438" s="4">
         <v>442</v>
       </c>
@@ -55941,7 +55964,7 @@
         <v>18</v>
       </c>
       <c r="I1438" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J1438" s="4" t="s">
         <v>1405</v>
@@ -55949,14 +55972,8 @@
       <c r="K1438" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="L1438" s="4" t="s">
-        <v>1629</v>
-      </c>
-      <c r="M1438" s="4" t="s">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="1439" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1439" s="4">
         <v>443</v>
       </c>
@@ -55990,14 +56007,8 @@
       <c r="K1439" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1439" s="4" t="s">
-        <v>1631</v>
-      </c>
-      <c r="M1439" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1440" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1440" s="4">
         <v>444</v>
       </c>
@@ -56031,14 +56042,8 @@
       <c r="K1440" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="L1440" s="4" t="s">
-        <v>1633</v>
-      </c>
-      <c r="M1440" s="4" t="s">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="1441" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1441" s="4">
         <v>445</v>
       </c>
@@ -56072,14 +56077,8 @@
       <c r="K1441" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1441" s="4" t="s">
-        <v>1634</v>
-      </c>
-      <c r="M1441" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1442" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1442" s="4">
         <v>447</v>
       </c>
@@ -56113,14 +56112,8 @@
       <c r="K1442" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="L1442" s="4" t="s">
-        <v>1635</v>
-      </c>
-      <c r="M1442" s="4" t="s">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="1443" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1443" s="4">
         <v>449</v>
       </c>
@@ -56154,14 +56147,8 @@
       <c r="K1443" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1443" s="4" t="s">
-        <v>1636</v>
-      </c>
-      <c r="M1443" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1444" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1444" s="4">
         <v>450</v>
       </c>
@@ -56195,14 +56182,8 @@
       <c r="K1444" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1444" s="4" t="s">
-        <v>1637</v>
-      </c>
-      <c r="M1444" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1445" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1445" s="4">
         <v>452</v>
       </c>
@@ -56236,14 +56217,8 @@
       <c r="K1445" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="L1445" s="4" t="s">
-        <v>1638</v>
-      </c>
-      <c r="M1445" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1446" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1446" s="4">
         <v>453</v>
       </c>
@@ -56277,14 +56252,8 @@
       <c r="K1446" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1446" s="4" t="s">
-        <v>1639</v>
-      </c>
-      <c r="M1446" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1447" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1447" s="4">
         <v>454</v>
       </c>
@@ -56318,14 +56287,8 @@
       <c r="K1447" s="8" t="s">
         <v>1441</v>
       </c>
-      <c r="L1447" s="4" t="s">
-        <v>1640</v>
-      </c>
-      <c r="M1447" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1448" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1448" s="4">
         <v>455</v>
       </c>
@@ -56359,14 +56322,8 @@
       <c r="K1448" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1448" s="4" t="s">
-        <v>1641</v>
-      </c>
-      <c r="M1448" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1449" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1449" s="4">
         <v>456</v>
       </c>
@@ -56400,14 +56357,8 @@
       <c r="K1449" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1449" s="4" t="s">
-        <v>1642</v>
-      </c>
-      <c r="M1449" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1450" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1450" s="4">
         <v>457</v>
       </c>
@@ -56441,14 +56392,8 @@
       <c r="K1450" s="8" t="s">
         <v>1440</v>
       </c>
-      <c r="L1450" s="4" t="s">
-        <v>1643</v>
-      </c>
-      <c r="M1450" s="4" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="1451" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1451" s="4">
         <v>458</v>
       </c>
@@ -56468,7 +56413,7 @@
         <v>16</v>
       </c>
       <c r="G1451" s="8" t="s">
-        <v>1644</v>
+        <v>1629</v>
       </c>
       <c r="H1451" s="4" t="s">
         <v>13</v>
@@ -56481,6 +56426,496 @@
       </c>
       <c r="K1451" s="8" t="s">
         <v>1441</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1452" s="4">
+        <v>459</v>
+      </c>
+      <c r="B1452" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1452" s="8">
+        <v>121466</v>
+      </c>
+      <c r="D1452" s="8" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E1452" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1452" s="8" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H1452" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1452" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1452" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1452" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1453" s="4">
+        <v>460</v>
+      </c>
+      <c r="B1453" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1453" s="8">
+        <v>104421</v>
+      </c>
+      <c r="D1453" s="8" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E1453" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1453" s="8" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H1453" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1453" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1453" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1453" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1454" s="4">
+        <v>461</v>
+      </c>
+      <c r="B1454" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1454" s="8">
+        <v>122786</v>
+      </c>
+      <c r="D1454" s="8" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E1454" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1454" s="8" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H1454" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1454" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1454" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1454" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1455" s="4">
+        <v>462</v>
+      </c>
+      <c r="B1455" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1455" s="8">
+        <v>119382</v>
+      </c>
+      <c r="D1455" s="8" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E1455" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1455" s="8" t="s">
+        <v>1640</v>
+      </c>
+      <c r="H1455" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1455" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1455" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1455" s="8" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1456" s="4">
+        <v>463</v>
+      </c>
+      <c r="B1456" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1456" s="8">
+        <v>119637</v>
+      </c>
+      <c r="D1456" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1456" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1456" s="8" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H1456" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1456" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1456" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1456" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1457" s="4">
+        <v>464</v>
+      </c>
+      <c r="B1457" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1457" s="8">
+        <v>112647</v>
+      </c>
+      <c r="D1457" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1457" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1457" s="8" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H1457" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1457" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1457" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1457" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1458" s="4">
+        <v>465</v>
+      </c>
+      <c r="B1458" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1458" s="8">
+        <v>115619</v>
+      </c>
+      <c r="D1458" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1458" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="F1458" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1458" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="H1458" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1458" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1458" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1458" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1459" s="4">
+        <v>466</v>
+      </c>
+      <c r="B1459" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1459" s="8">
+        <v>113855</v>
+      </c>
+      <c r="D1459" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1459" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1459" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1459" s="8" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H1459" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1459" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1459" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1459" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1460" s="4">
+        <v>467</v>
+      </c>
+      <c r="B1460" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1460" s="8">
+        <v>112512</v>
+      </c>
+      <c r="D1460" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1460" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="F1460" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1460" s="8" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H1460" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1460" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1460" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1460" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1461" s="4">
+        <v>468</v>
+      </c>
+      <c r="B1461" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1461" s="8">
+        <v>97448</v>
+      </c>
+      <c r="D1461" s="8" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E1461" s="8" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F1461" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1461" s="8" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1461" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1461" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1461" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1461" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1462" s="4">
+        <v>469</v>
+      </c>
+      <c r="B1462" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1462" s="8">
+        <v>104427</v>
+      </c>
+      <c r="D1462" s="8" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E1462" s="8" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F1462" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1462" s="8" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H1462" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1462" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1462" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1462" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1463" s="4">
+        <v>470</v>
+      </c>
+      <c r="B1463" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1463" s="8">
+        <v>116197</v>
+      </c>
+      <c r="D1463" s="8" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E1463" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1463" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1463" s="8" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H1463" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1463" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1463" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1463" s="8" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1464" s="4">
+        <v>471</v>
+      </c>
+      <c r="B1464" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1464" s="8">
+        <v>117844</v>
+      </c>
+      <c r="D1464" s="8" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E1464" s="8" t="s">
+        <v>1635</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1464" s="8" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1464" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1464" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1464" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1464" s="8" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1465" s="4">
+        <v>472</v>
+      </c>
+      <c r="B1465" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1465" s="8">
+        <v>104357</v>
+      </c>
+      <c r="D1465" s="8" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E1465" s="8" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1465" s="8" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H1465" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1465" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1465" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1465" s="8" t="s">
+        <v>1442</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="705" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{270A3ED1-7987-4D50-A7AC-16BA09B62C38}"/>
+  <xr:revisionPtr revIDLastSave="907" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD3975A2-3AB1-4DF1-A5DB-71AE92081015}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="1920" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11738" uniqueCount="1651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12218" uniqueCount="1741">
   <si>
     <t>ID</t>
   </si>
@@ -5180,6 +5180,288 @@
   </si>
   <si>
     <t>Porque vocês estão muito desorganizados, enviam o técnico sem fazer uma programação antecipada, sem avisar, e todas as vezes, nesses ultimos meses, tem pego nós desprevenidos, isso demonstra uma total falta de organização e respeito com o cliente!</t>
+  </si>
+  <si>
+    <t>FRQ MOGI GUACU SP R02</t>
+  </si>
+  <si>
+    <t>FRQ BRAGANCA PAULISTA SP R06</t>
+  </si>
+  <si>
+    <t>FRQ FLORIPA SC R01 - MATRIZ</t>
+  </si>
+  <si>
+    <t>FRQ CAMPINAS R03</t>
+  </si>
+  <si>
+    <t>FRQ CURITIBA PR R06</t>
+  </si>
+  <si>
+    <t>Manutenção Preventiva</t>
+  </si>
+  <si>
+    <t>Troca</t>
+  </si>
+  <si>
+    <t>Somos clientes antigos.
+Após a troca do filtro na semana passada (13/8), água esta com um gosto horrível!
+De química!
+Sempre prezamos pelo sabor da nossa água, mas desta vez!
+Que arrependimento em realizar a manutenção.
+Pra consertar agenda é super complicada.
+Questionamos até se este filtro novo mesmo!</t>
+  </si>
+  <si>
+    <t>Dei essa classificação por conta da resolução da questão da troca do bebedouro, muito tempo pra esperar a solução do problema, quanto ao técnico dou 10, abriu o bebedouro, limpou, explicou e até mesmo disse que falaria com supervisor para adiantar a troca, por meu marido já cancelaria pq 30 dias pra resolver é muito tempo .</t>
+  </si>
+  <si>
+    <t>confusão nos pagamentos da transição, duas visitas não realizadas (10h de espera em vão)</t>
+  </si>
+  <si>
+    <t>Boa tarde,
+Embora o atendimento da equipe de manutenção tenha sido satisfatório, o problema persiste, pois os reparos realizados não estão solucionando a falha de forma satisfatória  .Já solicitei anteriormente a substituição do aparelho, que apresenta desgaste decorrente do tempo de uso e do funcionamento contínuo, mas até o momento não fui atendido.
+Continuo aguardando obg</t>
+  </si>
+  <si>
+    <t>Pela segunda vez recebo a visita técnica para reparo e os técnicos não resolveram os problemas,  mesmo eu informando na chamada o tipo de problema. Estou sem utilizar o filtro a mais de 15 dias. Ficaram de ir trocar o filtro. No ano passado foi igual o mesmo problema!</t>
+  </si>
+  <si>
+    <t>O serviço foi agendado para a sexta feira última, não apareceu ninguém no fia combinado, além disso vocês  me informaram que a visita tinha sido feita.</t>
+  </si>
+  <si>
+    <t>Aparelho não sai agua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A conta não chega ,atrasa tudo,quero cancelar </t>
+  </si>
+  <si>
+    <t>O técnico veio fora do horario previsto.</t>
+  </si>
+  <si>
+    <t>Péssimo. O técnico foi 2x na minha casa e a minha água continua quente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de item para fazer manutenção exemplo: FILTRO
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde. Eu ja fui cliente por 7 anos no RJ e tinha esse mesmo modelo em casa, o filtro foi instalado ontem e hj qdo comecei a usar verifiquei que na retirada da água, esta fazendo um barulho horrível na hora que aperta o botão para parar a água. Nao sei se é defeito, mas muito estranho. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O equipamento está fazendo um barrulho diferente em funcionamento, e a pessoa que foi dar a manutenção não fez nada, disse que é normal. Achei muito grosseiro da parte dele, e também está claro, que o equipamento não está normal e que vai dar mais problemas se não for resolvido. 
+Detalhe: eu tenho o contrato do equipamento para meus avós, então, talvez ele teve o descaso por ser idosos. </t>
+  </si>
+  <si>
+    <t>Eu solicitei a manutenção semestral porque não houve da parte de vocês manifestação para esse serviço. Aproveitei e informei que meu purificador estava com o fluxo de água comprometido e que a água não estava saindo gelada somente fresca. O tecnico foi fazer o serviço e a agua continua tépida e o fluxo melhorou mas não voltou ao normal. Solicitei nova visita e remarcaram para o dia 26 de agosto!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serviço péssimo. A máquina está com problema sem funcionar desde o dia que foi instalada e não resolvem. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fizemos agendamento com um mês de antecedência e não compareceram, tivemos que remarcar a visita do técnico não durou 5 minutos. Não passou nenhum retorno sobre a visita, nem nada. Sistema falho para tentar avisar que não veio ninguém na visita, falava repetidamente da visita que já havia passado a data. </t>
+  </si>
+  <si>
+    <t>Péssimo atendimento. Foi marcado para o dia 12/08 vieram no dia 11/08 sem aviso prévio. 
+ Funcionário irritado, pois foi perguntado pque da mudança respondeu: se a Sra. quiser eu não faço nada e volto amanhã se der. ?????</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnico foi em casa, nao resolveu o problema, deixou o filtro vazando dizendo que voltaria na segunda feira e nunca mais voltou.
+Meu filtro agora continua sem agua gelada e passou a alagar minha cozinha </t>
+  </si>
+  <si>
+    <t>o técnico não compareceu para realizar o serviço.</t>
+  </si>
+  <si>
+    <t>Mais uma vez o problema não foi resolvido. E não tive resposta inclusive sobre o móvel danificado.</t>
+  </si>
+  <si>
+    <t>Não gostei do serviço prestado. O técnico não encaixou a frente do meu purificador corretamente! E assim a bandeja de suporte para copos e garrafas também fica mal encaixada. Um absurdo! Pois penso que o técnico não deveria terminar o serviço e ir embora antes de verificar se tudo estava perfeitamente encaixado! Fiquei muito insatisfeita!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não foi deixado nenhum documento ou relatório do que foi feito. O recibo apenas pediu a Recepcionista para sssinar e não deixou nada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O técnico nunca vem no dia marcado e termina atrapalhando a rotina ou a manutenção não ocorre </t>
+  </si>
+  <si>
+    <t>Não aconteceu. Fiquei esperando o técnico que não apareceu, não deu satisfação. No dia seguinte entrei em contato e simplesmente fui informado que nada poderia ser feito, pois a empresa de assistência é "terceirizada". Pergunto: o que eu tenho a ver com a forma de trabalho de vocês? Lamentável. Estou até agora esperando algum contato.</t>
+  </si>
+  <si>
+    <t>Os motivos foram declarados na central de atendimento.</t>
+  </si>
+  <si>
+    <t>FALTA DE TRANSPARENCIA COM O CLIENTE</t>
+  </si>
+  <si>
+    <t>PORQUE AGENDAMOS PARA A PARTE DA TARDE E O TÉCNICO VEIO AS 10 HS DA MANHÃ….</t>
+  </si>
+  <si>
+    <t>Péssimo agendamento. Não cumprem prazo. Os profissionais não têm hora pra chegar, independentemente de ter havido, previamente, um agendamento, fora a expectativa de não comparecerem no dia marcado, como aconteceu, recentemente, comigo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muito ruim , estava agendado entre 8:00 e 13:00 chegou 15:00 além disso produto já parou de funcionar </t>
+  </si>
+  <si>
+    <t>O purificador com vazamento por baixo o técnico já veio duas vezes e não resolveu. Tem danos no móvel.</t>
+  </si>
+  <si>
+    <t>bom dia entalação errada, comuniquei ate agora não resolveu&amp;gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Já alugo o aparelho há muito anos,mas tive problemas na última visita técnica agendada. O técnico não tinha a senha que foi enviada. Achei muita deorganização.</t>
+  </si>
+  <si>
+    <t>Não gostei do atendimento  que não durou nem 5 minutos, a manutenção já foi melhor, hj só cola selo</t>
+  </si>
+  <si>
+    <t>enviam técnico sem avisar, pegam desprevenido</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>conta muito caro + não gela + só robô</t>
+  </si>
+  <si>
+    <t>REVISAR</t>
+  </si>
+  <si>
+    <t>deixaram água embaixo e não avisaram</t>
+  </si>
+  <si>
+    <t>pede fatura sem senha, não é atendido</t>
+  </si>
+  <si>
+    <t>sem crachá e sem uniforme</t>
+  </si>
+  <si>
+    <t>deixou sujeira e plástico no chão</t>
+  </si>
+  <si>
+    <t>gosto de metal + esquentando muito</t>
+  </si>
+  <si>
+    <t>não avaliou necessidade de troca de peças</t>
+  </si>
+  <si>
+    <t>não trocou filtro, ficou 1 ano</t>
+  </si>
+  <si>
+    <t>agendei 2 vezes e não apareceu ninguém</t>
+  </si>
+  <si>
+    <t>disseram que voltariam e não vieram</t>
+  </si>
+  <si>
+    <t>não veio o elemento filtrante + água podre</t>
+  </si>
+  <si>
+    <t>não atendem, pedi o atendimento</t>
+  </si>
+  <si>
+    <t>falta de compromisso com horário agendado</t>
+  </si>
+  <si>
+    <t>água com gosto de química após troca</t>
+  </si>
+  <si>
+    <t>30 dias esperando troca do bebedouro</t>
+  </si>
+  <si>
+    <t>duas visitas não realizadas, 10h de espera</t>
+  </si>
+  <si>
+    <t>reparos não solucionam, troca não atendida</t>
+  </si>
+  <si>
+    <t>segunda vez sem resolver, mesmo problema</t>
+  </si>
+  <si>
+    <t>ninguém apareceu e informaram visita feita</t>
+  </si>
+  <si>
+    <t>aparelho não sai água</t>
+  </si>
+  <si>
+    <t>conta não chega, quer cancelar</t>
+  </si>
+  <si>
+    <t>técnico veio fora do horário previsto</t>
+  </si>
+  <si>
+    <t>água continua quente após 2 visitas</t>
+  </si>
+  <si>
+    <t>falta de item para manutenção: filtro</t>
+  </si>
+  <si>
+    <t>barulho horrível ao apertar o botão</t>
+  </si>
+  <si>
+    <t>não fez nada pelo ruído + achei grosseiro</t>
+  </si>
+  <si>
+    <t>água continua tépida + fluxo comprometido</t>
+  </si>
+  <si>
+    <t>sem funcionar desde a instalação</t>
+  </si>
+  <si>
+    <t>preço alto</t>
+  </si>
+  <si>
+    <t>não compareceram + visita de 5 minutos</t>
+  </si>
+  <si>
+    <t>vieram um dia antes sem aviso + irritado</t>
+  </si>
+  <si>
+    <t>deixou o filtro vazando, alagou cozinha</t>
+  </si>
+  <si>
+    <t>técnico não compareceu</t>
+  </si>
+  <si>
+    <t>mais uma vez o problema não foi resolvido</t>
+  </si>
+  <si>
+    <t>não encaixou a frente do purificador</t>
+  </si>
+  <si>
+    <t>não deixou relatório nem comprovante</t>
+  </si>
+  <si>
+    <t>nunca vem no dia marcado</t>
+  </si>
+  <si>
+    <t>não aconteceu, técnico não apareceu</t>
+  </si>
+  <si>
+    <t>motivos declarados na central</t>
+  </si>
+  <si>
+    <t>falta de transparência com o cliente</t>
+  </si>
+  <si>
+    <t>agendado à tarde, veio 10h da manhã</t>
+  </si>
+  <si>
+    <t>não comparecem no dia marcado</t>
+  </si>
+  <si>
+    <t>agendado 8-13h chegou 15h + parou de funcionar</t>
+  </si>
+  <si>
+    <t>vazamento por baixo, 2 visitas sem resolver</t>
+  </si>
+  <si>
+    <t>instalação errada, comuniquei e não resolveu</t>
+  </si>
+  <si>
+    <t>técnico não tinha a senha enviada</t>
+  </si>
+  <si>
+    <t>atendimento não durou 5 minutos, só cola selo</t>
   </si>
 </sst>
 </file>
@@ -5268,7 +5550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5296,6 +5578,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5621,7 +5906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1465"/>
+  <dimension ref="A1:M1513"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -56603,7 +56888,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1457" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1457" s="4">
         <v>464</v>
       </c>
@@ -56638,7 +56923,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1458" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1458" s="4">
         <v>465</v>
       </c>
@@ -56673,7 +56958,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1459" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1459" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1459" s="4">
         <v>466</v>
       </c>
@@ -56708,7 +56993,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1460" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1460" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1460" s="4">
         <v>467</v>
       </c>
@@ -56743,7 +57028,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1461" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1461" s="4">
         <v>468</v>
       </c>
@@ -56778,7 +57063,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1462" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1462" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1462" s="4">
         <v>469</v>
       </c>
@@ -56813,7 +57098,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1463" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1463" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1463" s="4">
         <v>470</v>
       </c>
@@ -56848,7 +57133,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="1464" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1464" s="4">
         <v>471</v>
       </c>
@@ -56883,7 +57168,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="1465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1465" s="4">
         <v>472</v>
       </c>
@@ -56916,6 +57201,1974 @@
       </c>
       <c r="K1465" s="8" t="s">
         <v>1442</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1466" s="4">
+        <v>473</v>
+      </c>
+      <c r="B1466" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1466" s="8">
+        <v>104357</v>
+      </c>
+      <c r="D1466" s="10">
+        <v>46246.477436666668</v>
+      </c>
+      <c r="E1466" s="8" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F1466" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1466" s="8" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H1466" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1466" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1466" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1466" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="L1466" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="M1466" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1467" s="4">
+        <v>474</v>
+      </c>
+      <c r="B1467" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1467" s="8">
+        <v>117844</v>
+      </c>
+      <c r="D1467" s="10">
+        <v>46246.860933148149</v>
+      </c>
+      <c r="E1467" s="8" t="s">
+        <v>1635</v>
+      </c>
+      <c r="F1467" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1467" s="8" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1467" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1467" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1467" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1467" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1467" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="M1467" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1468" s="4">
+        <v>475</v>
+      </c>
+      <c r="B1468" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1468" s="8">
+        <v>116197</v>
+      </c>
+      <c r="D1468" s="10">
+        <v>46247.73844645833</v>
+      </c>
+      <c r="E1468" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1468" s="8" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H1468" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1468" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1468" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1468" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1468" s="4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="M1468" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1469" s="4">
+        <v>476</v>
+      </c>
+      <c r="B1469" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1469" s="8">
+        <v>104427</v>
+      </c>
+      <c r="D1469" s="10">
+        <v>46247.761227499999</v>
+      </c>
+      <c r="E1469" s="8" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F1469" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1469" s="8" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H1469" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1469" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1469" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1469" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1469" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="M1469" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1470" s="4">
+        <v>477</v>
+      </c>
+      <c r="B1470" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1470" s="8">
+        <v>97448</v>
+      </c>
+      <c r="D1470" s="10">
+        <v>46247.76924115741</v>
+      </c>
+      <c r="E1470" s="8" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F1470" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1470" s="8" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1470" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1470" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1470" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1470" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1470" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="M1470" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1471" s="4">
+        <v>478</v>
+      </c>
+      <c r="B1471" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1471" s="8">
+        <v>112512</v>
+      </c>
+      <c r="D1471" s="10">
+        <v>46248.768450856478</v>
+      </c>
+      <c r="E1471" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="F1471" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1471" s="8" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H1471" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1471" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1471" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1471" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1471" s="4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M1471" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1472" s="4">
+        <v>479</v>
+      </c>
+      <c r="B1472" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1472" s="8">
+        <v>113855</v>
+      </c>
+      <c r="D1472" s="10">
+        <v>46248.78429275463</v>
+      </c>
+      <c r="E1472" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1472" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1472" s="8" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H1472" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1472" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1472" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1472" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1472" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="M1472" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1473" s="4">
+        <v>480</v>
+      </c>
+      <c r="B1473" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1473" s="8">
+        <v>115619</v>
+      </c>
+      <c r="D1473" s="10">
+        <v>46248.846609004628</v>
+      </c>
+      <c r="E1473" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1473" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="H1473" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1473" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1473" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1473" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1473" s="4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="M1473" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1474" s="4">
+        <v>481</v>
+      </c>
+      <c r="B1474" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1474" s="8">
+        <v>112647</v>
+      </c>
+      <c r="D1474" s="10">
+        <v>46248.886021979168</v>
+      </c>
+      <c r="E1474" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1474" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1474" s="8" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H1474" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1474" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1474" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1474" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1474" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="M1474" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1475" s="4">
+        <v>482</v>
+      </c>
+      <c r="B1475" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1475" s="8">
+        <v>119637</v>
+      </c>
+      <c r="D1475" s="10">
+        <v>46248.921772291673</v>
+      </c>
+      <c r="E1475" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1475" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1475" s="8" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H1475" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1475" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1475" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1475" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1475" s="4" t="s">
+        <v>1702</v>
+      </c>
+      <c r="M1475" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1476" s="4">
+        <v>483</v>
+      </c>
+      <c r="B1476" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1476" s="8">
+        <v>119382</v>
+      </c>
+      <c r="D1476" s="10">
+        <v>46249.484861122677</v>
+      </c>
+      <c r="E1476" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1476" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1476" s="8" t="s">
+        <v>1640</v>
+      </c>
+      <c r="H1476" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1476" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1476" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1476" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1476" s="4" t="s">
+        <v>1703</v>
+      </c>
+      <c r="M1476" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1477" s="4">
+        <v>484</v>
+      </c>
+      <c r="B1477" s="8" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C1477" s="8">
+        <v>122786</v>
+      </c>
+      <c r="D1477" s="10">
+        <v>46249.539972361112</v>
+      </c>
+      <c r="E1477" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="F1477" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1477" s="8" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H1477" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1477" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1477" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1477" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1477" s="4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="M1477" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1478" s="4">
+        <v>485</v>
+      </c>
+      <c r="B1478" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1478" s="8">
+        <v>104421</v>
+      </c>
+      <c r="D1478" s="10">
+        <v>46249.68085780093</v>
+      </c>
+      <c r="E1478" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="F1478" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1478" s="8" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H1478" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1478" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1478" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1478" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1478" s="4" t="s">
+        <v>1705</v>
+      </c>
+      <c r="M1478" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1479" s="4">
+        <v>486</v>
+      </c>
+      <c r="B1479" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1479" s="8">
+        <v>121466</v>
+      </c>
+      <c r="D1479" s="10">
+        <v>46249.716209664351</v>
+      </c>
+      <c r="E1479" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1479" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1479" s="8" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H1479" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1479" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1479" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1479" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1479" s="4" t="s">
+        <v>1706</v>
+      </c>
+      <c r="M1479" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1480" s="4">
+        <v>487</v>
+      </c>
+      <c r="B1480" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1480" s="8">
+        <v>121020</v>
+      </c>
+      <c r="D1480" s="10">
+        <v>46251.548014814813</v>
+      </c>
+      <c r="E1480" s="8" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F1480" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1480" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H1480" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1480" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1480" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1480" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1480" s="4" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M1480" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1481" s="4">
+        <v>488</v>
+      </c>
+      <c r="B1481" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1481" s="8">
+        <v>110872</v>
+      </c>
+      <c r="D1481" s="10">
+        <v>46251.59071384259</v>
+      </c>
+      <c r="E1481" s="8" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F1481" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1481" s="8" t="s">
+        <v>1659</v>
+      </c>
+      <c r="H1481" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1481" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1481" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1481" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1481" s="4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="M1481" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1482" s="4">
+        <v>489</v>
+      </c>
+      <c r="B1482" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1482" s="8">
+        <v>119549</v>
+      </c>
+      <c r="D1482" s="10">
+        <v>46251.595791782413</v>
+      </c>
+      <c r="E1482" s="8" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F1482" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1482" s="8" t="s">
+        <v>1660</v>
+      </c>
+      <c r="H1482" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1482" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1482" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1482" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1482" s="4" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M1482" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1483" s="4">
+        <v>490</v>
+      </c>
+      <c r="B1483" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1483" s="8">
+        <v>114435</v>
+      </c>
+      <c r="D1483" s="10">
+        <v>46251.644513576393</v>
+      </c>
+      <c r="E1483" s="8" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1483" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1483" s="8" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H1483" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1483" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1483" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1483" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1483" s="4" t="s">
+        <v>1710</v>
+      </c>
+      <c r="M1483" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1484" s="4">
+        <v>491</v>
+      </c>
+      <c r="B1484" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1484" s="8">
+        <v>116426</v>
+      </c>
+      <c r="D1484" s="10">
+        <v>46251.657401446762</v>
+      </c>
+      <c r="E1484" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1484" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1484" s="8" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H1484" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1484" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1484" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1484" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1484" s="4" t="s">
+        <v>1711</v>
+      </c>
+      <c r="M1484" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1485" s="4">
+        <v>492</v>
+      </c>
+      <c r="B1485" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1485" s="8">
+        <v>96354</v>
+      </c>
+      <c r="D1485" s="10">
+        <v>46251.660639374997</v>
+      </c>
+      <c r="E1485" s="8" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1485" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1485" s="8" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H1485" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1485" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1485" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1485" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1485" s="4" t="s">
+        <v>1712</v>
+      </c>
+      <c r="M1485" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1486" s="4">
+        <v>493</v>
+      </c>
+      <c r="B1486" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1486" s="8">
+        <v>116408</v>
+      </c>
+      <c r="D1486" s="10">
+        <v>46251.675366412041</v>
+      </c>
+      <c r="E1486" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1486" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1486" s="8" t="s">
+        <v>1664</v>
+      </c>
+      <c r="H1486" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1486" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1486" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1486" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1486" s="4" t="s">
+        <v>1713</v>
+      </c>
+      <c r="M1486" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1487" s="4">
+        <v>494</v>
+      </c>
+      <c r="B1487" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1487" s="8">
+        <v>123194</v>
+      </c>
+      <c r="D1487" s="10">
+        <v>46251.698660752307</v>
+      </c>
+      <c r="E1487" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1487" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1487" s="8" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H1487" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1487" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1487" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1487" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1487" s="4" t="s">
+        <v>1714</v>
+      </c>
+      <c r="M1487" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1488" s="4">
+        <v>495</v>
+      </c>
+      <c r="B1488" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1488" s="8">
+        <v>110065</v>
+      </c>
+      <c r="D1488" s="10">
+        <v>46251.738354201392</v>
+      </c>
+      <c r="E1488" s="8" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1488" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1488" s="8" t="s">
+        <v>1666</v>
+      </c>
+      <c r="H1488" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1488" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1488" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1488" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1488" s="4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="M1488" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1489" s="4">
+        <v>496</v>
+      </c>
+      <c r="B1489" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1489" s="8">
+        <v>119204</v>
+      </c>
+      <c r="D1489" s="10">
+        <v>46251.839549166667</v>
+      </c>
+      <c r="E1489" s="8" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F1489" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1489" s="8" t="s">
+        <v>1667</v>
+      </c>
+      <c r="H1489" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1489" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1489" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1489" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1489" s="4" t="s">
+        <v>1716</v>
+      </c>
+      <c r="M1489" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1490" s="4">
+        <v>497</v>
+      </c>
+      <c r="B1490" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1490" s="8">
+        <v>116632</v>
+      </c>
+      <c r="D1490" s="10">
+        <v>46252.58895109954</v>
+      </c>
+      <c r="E1490" s="8" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1490" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1490" s="8" t="s">
+        <v>1668</v>
+      </c>
+      <c r="H1490" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1490" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1490" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1490" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1490" s="4" t="s">
+        <v>1717</v>
+      </c>
+      <c r="M1490" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1491" s="4">
+        <v>498</v>
+      </c>
+      <c r="B1491" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1491" s="8">
+        <v>122445</v>
+      </c>
+      <c r="D1491" s="10">
+        <v>46252.756570995371</v>
+      </c>
+      <c r="E1491" s="8" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1491" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1491" s="8" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H1491" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1491" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1491" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1491" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1491" s="4" t="s">
+        <v>1718</v>
+      </c>
+      <c r="M1491" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1492" s="4">
+        <v>499</v>
+      </c>
+      <c r="B1492" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1492" s="8">
+        <v>121871</v>
+      </c>
+      <c r="D1492" s="10">
+        <v>46252.826207824073</v>
+      </c>
+      <c r="E1492" s="8" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F1492" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1492" s="8" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H1492" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1492" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1492" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1492" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1492" s="4" t="s">
+        <v>1719</v>
+      </c>
+      <c r="M1492" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1493" s="4">
+        <v>500</v>
+      </c>
+      <c r="B1493" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1493" s="8">
+        <v>119520</v>
+      </c>
+      <c r="D1493" s="10">
+        <v>46252.867391435182</v>
+      </c>
+      <c r="E1493" s="8" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1493" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1493" s="8" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H1493" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1493" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1493" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1493" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1493" s="4" t="s">
+        <v>1720</v>
+      </c>
+      <c r="M1493" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1494" s="4">
+        <v>501</v>
+      </c>
+      <c r="B1494" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1494" s="8">
+        <v>120161</v>
+      </c>
+      <c r="D1494" s="10">
+        <v>46252.950519965278</v>
+      </c>
+      <c r="E1494" s="8" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F1494" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1494" s="8" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H1494" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1494" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1494" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1494" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1494" s="4" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M1494" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1495" s="4">
+        <v>502</v>
+      </c>
+      <c r="B1495" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1495" s="8">
+        <v>118051</v>
+      </c>
+      <c r="D1495" s="10">
+        <v>46253.711167974543</v>
+      </c>
+      <c r="E1495" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1495" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1495" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H1495" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1495" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1495" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1495" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1495" s="4" t="s">
+        <v>1722</v>
+      </c>
+      <c r="M1495" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1496" s="4">
+        <v>503</v>
+      </c>
+      <c r="B1496" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1496" s="8">
+        <v>118660</v>
+      </c>
+      <c r="D1496" s="10">
+        <v>46253.793205069444</v>
+      </c>
+      <c r="E1496" s="8" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F1496" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1496" s="8" t="s">
+        <v>1673</v>
+      </c>
+      <c r="H1496" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1496" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1496" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1496" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1496" s="4" t="s">
+        <v>1723</v>
+      </c>
+      <c r="M1496" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1497" s="4">
+        <v>504</v>
+      </c>
+      <c r="B1497" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1497" s="8">
+        <v>119228</v>
+      </c>
+      <c r="D1497" s="10">
+        <v>46253.828614652783</v>
+      </c>
+      <c r="E1497" s="8" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F1497" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1497" s="8" t="s">
+        <v>1674</v>
+      </c>
+      <c r="H1497" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1497" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1497" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1497" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1497" s="4" t="s">
+        <v>1724</v>
+      </c>
+      <c r="M1497" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1498" s="4">
+        <v>505</v>
+      </c>
+      <c r="B1498" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1498" s="8">
+        <v>118868</v>
+      </c>
+      <c r="D1498" s="10">
+        <v>46254.568633726849</v>
+      </c>
+      <c r="E1498" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1498" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1498" s="8" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H1498" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1498" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1498" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1498" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1498" s="4" t="s">
+        <v>1725</v>
+      </c>
+      <c r="M1498" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1499" s="4">
+        <v>506</v>
+      </c>
+      <c r="B1499" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1499" s="8">
+        <v>112487</v>
+      </c>
+      <c r="D1499" s="10">
+        <v>46254.612892476849</v>
+      </c>
+      <c r="E1499" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F1499" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1499" s="8" t="s">
+        <v>1676</v>
+      </c>
+      <c r="H1499" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1499" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1499" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1499" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1499" s="4" t="s">
+        <v>1726</v>
+      </c>
+      <c r="M1499" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1500" s="4">
+        <v>507</v>
+      </c>
+      <c r="B1500" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1500" s="8">
+        <v>120111</v>
+      </c>
+      <c r="D1500" s="10">
+        <v>46254.670405370372</v>
+      </c>
+      <c r="E1500" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1500" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1500" s="8" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H1500" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1500" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1500" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1500" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1500" s="4" t="s">
+        <v>1727</v>
+      </c>
+      <c r="M1500" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1501" s="4">
+        <v>508</v>
+      </c>
+      <c r="B1501" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1501" s="8">
+        <v>109186</v>
+      </c>
+      <c r="D1501" s="10">
+        <v>46254.880398946763</v>
+      </c>
+      <c r="E1501" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F1501" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1501" s="8" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H1501" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1501" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1501" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1501" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1501" s="4" t="s">
+        <v>1728</v>
+      </c>
+      <c r="M1501" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1502" s="4">
+        <v>509</v>
+      </c>
+      <c r="B1502" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1502" s="8">
+        <v>119191</v>
+      </c>
+      <c r="D1502" s="10">
+        <v>46255.64077391204</v>
+      </c>
+      <c r="E1502" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F1502" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1502" s="8" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H1502" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1502" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1502" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1502" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1502" s="4" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M1502" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1503" s="4">
+        <v>510</v>
+      </c>
+      <c r="B1503" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1503" s="8">
+        <v>115367</v>
+      </c>
+      <c r="D1503" s="10">
+        <v>46255.645053310189</v>
+      </c>
+      <c r="E1503" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1503" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1503" s="8" t="s">
+        <v>1680</v>
+      </c>
+      <c r="H1503" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1503" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1503" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1503" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1503" s="4" t="s">
+        <v>1730</v>
+      </c>
+      <c r="M1503" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1504" s="4">
+        <v>511</v>
+      </c>
+      <c r="B1504" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1504" s="8">
+        <v>117177</v>
+      </c>
+      <c r="D1504" s="10">
+        <v>46255.649247083333</v>
+      </c>
+      <c r="E1504" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1504" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1504" s="8" t="s">
+        <v>1681</v>
+      </c>
+      <c r="H1504" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1504" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1504" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1504" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1504" s="4" t="s">
+        <v>1731</v>
+      </c>
+      <c r="M1504" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1505" s="4">
+        <v>512</v>
+      </c>
+      <c r="B1505" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1505" s="8">
+        <v>123664</v>
+      </c>
+      <c r="D1505" s="10">
+        <v>46255.673882916657</v>
+      </c>
+      <c r="E1505" s="8" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F1505" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1505" s="8" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H1505" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1505" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1505" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1505" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1505" s="4" t="s">
+        <v>1732</v>
+      </c>
+      <c r="M1505" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1506" s="4">
+        <v>513</v>
+      </c>
+      <c r="B1506" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1506" s="8">
+        <v>105564</v>
+      </c>
+      <c r="D1506" s="10">
+        <v>46255.75913697917</v>
+      </c>
+      <c r="E1506" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1506" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1506" s="8" t="s">
+        <v>1683</v>
+      </c>
+      <c r="H1506" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1506" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1506" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1506" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1506" s="4" t="s">
+        <v>1733</v>
+      </c>
+      <c r="M1506" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1507" s="4">
+        <v>514</v>
+      </c>
+      <c r="B1507" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1507" s="8">
+        <v>118216</v>
+      </c>
+      <c r="D1507" s="10">
+        <v>46255.769036481477</v>
+      </c>
+      <c r="E1507" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F1507" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1507" s="8" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H1507" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1507" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1507" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1507" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1507" s="4" t="s">
+        <v>1734</v>
+      </c>
+      <c r="M1507" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1508" s="4">
+        <v>515</v>
+      </c>
+      <c r="B1508" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1508" s="8">
+        <v>117952</v>
+      </c>
+      <c r="D1508" s="10">
+        <v>46255.784961990743</v>
+      </c>
+      <c r="E1508" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1508" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1508" s="8" t="s">
+        <v>1685</v>
+      </c>
+      <c r="H1508" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1508" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1508" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1508" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1508" s="4" t="s">
+        <v>1735</v>
+      </c>
+      <c r="M1508" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1509" s="4">
+        <v>516</v>
+      </c>
+      <c r="B1509" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1509" s="8">
+        <v>119350</v>
+      </c>
+      <c r="D1509" s="10">
+        <v>46256.386197175932</v>
+      </c>
+      <c r="E1509" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="F1509" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1509" s="8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="H1509" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1509" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1509" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1509" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1509" s="4" t="s">
+        <v>1736</v>
+      </c>
+      <c r="M1509" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1510" s="4">
+        <v>517</v>
+      </c>
+      <c r="B1510" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1510" s="8">
+        <v>118904</v>
+      </c>
+      <c r="D1510" s="10">
+        <v>46256.60289790509</v>
+      </c>
+      <c r="E1510" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1510" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1510" s="8" t="s">
+        <v>1687</v>
+      </c>
+      <c r="H1510" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1510" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1510" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1510" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1510" s="4" t="s">
+        <v>1737</v>
+      </c>
+      <c r="M1510" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1511" s="4">
+        <v>518</v>
+      </c>
+      <c r="B1511" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1511" s="8">
+        <v>125265</v>
+      </c>
+      <c r="D1511" s="10">
+        <v>46256.629825138887</v>
+      </c>
+      <c r="E1511" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1511" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1511" s="8" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H1511" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1511" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1511" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1511" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1511" s="4" t="s">
+        <v>1738</v>
+      </c>
+      <c r="M1511" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1512" s="4">
+        <v>519</v>
+      </c>
+      <c r="B1512" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1512" s="8">
+        <v>127160</v>
+      </c>
+      <c r="D1512" s="10">
+        <v>46256.844575266201</v>
+      </c>
+      <c r="E1512" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1512" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1512" s="8" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H1512" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1512" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1512" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1512" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1512" s="4" t="s">
+        <v>1739</v>
+      </c>
+      <c r="M1512" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1513" s="4">
+        <v>520</v>
+      </c>
+      <c r="B1513" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1513" s="8">
+        <v>114540</v>
+      </c>
+      <c r="D1513" s="10">
+        <v>46257.211157604157</v>
+      </c>
+      <c r="E1513" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1513" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1513" s="8" t="s">
+        <v>1690</v>
+      </c>
+      <c r="H1513" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1513" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1513" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1513" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1513" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="M1513" s="4" t="s">
+        <v>1692</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="907" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD3975A2-3AB1-4DF1-A5DB-71AE92081015}"/>
+  <xr:revisionPtr revIDLastSave="964" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56139A71-272B-4544-BA3D-179BB2D66D37}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="1920" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12218" uniqueCount="1741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12338" uniqueCount="1765">
   <si>
     <t>ID</t>
   </si>
@@ -5463,11 +5463,104 @@
   <si>
     <t>atendimento não durou 5 minutos, só cola selo</t>
   </si>
+  <si>
+    <t>Porque o tecnico não se preocupou em resolver algumas das nossas reclamações.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ .
+Porque o serviço prestado esta muito aquem do foi vendido no contrato. O aparelho apresentou problema fiz o chamado para assistencia técnica e desde a primeira visita o técnico solicitou a troca do aparelho, já retornou mais uma vez e até a presente data sigo com o aparelho operando com defeito. Equipamento oferecido em conbtrato com água gelada e gaseificada, hoje estou bebendo agua natural. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou com um problema no meu purificador, recorrente,a quase um ano! Sou cliente a mais de cinco anos, já solicitei a troca do mesmo e não fui atendido!!!!
+</t>
+  </si>
+  <si>
+    <t>Solicitamos reparo em um purificador que estava vazando, depois de demorar muito foi efetuada a substituição. Todavia, no mesmo dia identificamos que o equipamento "novo" não estava gelando e solicitamos o reparo. Faz mais de um mês que não temos água gelada. Não é admissível, visto que o propósito de se locar um equipamento é ter tranquilidade nas manuteções periódicas e emergenciais. Tinha-mos dois contratos e um já cancelamos. Em breve cancelaremos o outro caso o serviço continue precário.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque o serviço de vocês continua péssimo. Agendei para o período da tarde, o técnico veio de manhã. A sorte é que a minha filha ainda nao tinha saído. 
+</t>
+  </si>
+  <si>
+    <t>TIVEMOS QUE CHAMAR O TECNICO 2 VEZES E MESMO ASSIM O FILTRO CONTINUA VAZANDO.</t>
+  </si>
+  <si>
+    <t>Eu agendei para o período da tarde e o técnico veio por volta das 11h da manhã.
+Isto demonstra a desorganização da empresa. Dois agendamentos não atendidos e um terceiro atendido fora do horário agendado.</t>
+  </si>
+  <si>
+    <t>O tecnico nem veio! Já reclamei duas vezes que o filtro pinga, inclusive com videos enviados e depois de um dia para de pingar. o técnico veio e não fez nada.</t>
+  </si>
+  <si>
+    <t>A técnica chegou às 15:40h,  partir do que copio aqui a seguir, porque será que minha avaliação foi essa?????
+[11:10, 11/08/2026] Ju: Certo, então para confirmar você deseja uma visita técnica no seguinte período:
+Dia da Visita: Segunda-feira
+Data da Visita: 24/08/2026
+Período da Visita: Manhã - Entre 08h e 13h
+É isso mesmo?
+Por gentileza, me responda com sim ou não
+[11:10, 11/08/2026] Ju: ✅ A visita técnica foi agendada com sucesso. 
+📝 É importante que você anote o número da ordem de serviço:  00274421 e a sua senha de atendimento: 182295. 
+Outras informações importantes: 
+Nesta visita, o elemento filtrante somente será trocado se o teste de qualidade da água for reprovado pelo técnico.
+É necessário que alguém maior de 18 anos esteja no local para acompanhar o técnico no momento da visita.
+💡 Ah, e caso você não precise mais da visita do técnico ou quiser reagendá-la, entre em contato conosco. 😉</t>
+  </si>
+  <si>
+    <t>muitissimo caro</t>
+  </si>
+  <si>
+    <t>entrei em contato hoje com vocês, ninguem a apareceu aqui e no sistema consta que foi visitado sim. porem, nem no filtro foi trocado a etiqueta de validade da manutenção</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ficou atrasada a visita, saiu do conserto com gosto de metal ainda no purificador. </t>
+  </si>
+  <si>
+    <t>técnico não resolveu as reclamações</t>
+  </si>
+  <si>
+    <t>troca solicitada, 2 visitas, defeito persiste</t>
+  </si>
+  <si>
+    <t>problema recorrente há quase um ano</t>
+  </si>
+  <si>
+    <t>equipamento novo não gela + demora</t>
+  </si>
+  <si>
+    <t>agendou tarde, técnico veio de manhã</t>
+  </si>
+  <si>
+    <t>2 visitas e filtro continua vazando</t>
+  </si>
+  <si>
+    <t>veio 11h para tarde + 2 agendamentos não atendidos</t>
+  </si>
+  <si>
+    <t>técnico veio e não fez nada, filtro pinga</t>
+  </si>
+  <si>
+    <t>agendado 8-13h, técnica chegou 15:40h</t>
+  </si>
+  <si>
+    <t>muitíssimo caro</t>
+  </si>
+  <si>
+    <t>ninguém apareceu, sistema consta visitado</t>
+  </si>
+  <si>
+    <t>gosto de metal após conserto + visita atrasada</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5550,7 +5643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5580,6 +5673,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5884,7 +5980,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="8">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="10">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -5906,7 +6002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1513"/>
+  <dimension ref="A1:M1525"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -59171,6 +59267,498 @@
         <v>1692</v>
       </c>
     </row>
+    <row r="1514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1514" s="4">
+        <v>521</v>
+      </c>
+      <c r="B1514" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1514" s="8">
+        <v>114326</v>
+      </c>
+      <c r="D1514" s="11">
+        <v>46258.523561828697</v>
+      </c>
+      <c r="E1514" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1514" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1514" s="8" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H1514" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1514" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1514" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1514" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1514" s="4" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M1514" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1515" s="4">
+        <v>522</v>
+      </c>
+      <c r="B1515" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1515" s="8">
+        <v>124580</v>
+      </c>
+      <c r="D1515" s="11">
+        <v>46258.779456412027</v>
+      </c>
+      <c r="E1515" s="8" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F1515" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1515" s="8" t="s">
+        <v>1742</v>
+      </c>
+      <c r="H1515" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1515" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1515" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1515" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1515" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="M1515" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1516" s="4">
+        <v>523</v>
+      </c>
+      <c r="B1516" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1516" s="8">
+        <v>129091</v>
+      </c>
+      <c r="D1516" s="11">
+        <v>46258.838097372682</v>
+      </c>
+      <c r="E1516" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F1516" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1516" s="8" t="s">
+        <v>1743</v>
+      </c>
+      <c r="H1516" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1516" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1516" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1516" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1516" s="4" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M1516" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1517" s="4">
+        <v>524</v>
+      </c>
+      <c r="B1517" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1517" s="8">
+        <v>127403</v>
+      </c>
+      <c r="D1517" s="11">
+        <v>46259.595003784721</v>
+      </c>
+      <c r="E1517" s="8" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F1517" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1517" s="8" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H1517" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1517" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1517" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1517" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1517" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="M1517" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1518" s="4">
+        <v>525</v>
+      </c>
+      <c r="B1518" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1518" s="8">
+        <v>119438</v>
+      </c>
+      <c r="D1518" s="11">
+        <v>46259.967046863429</v>
+      </c>
+      <c r="E1518" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1518" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1518" s="8" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H1518" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1518" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1518" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1518" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1518" s="4" t="s">
+        <v>1757</v>
+      </c>
+      <c r="M1518" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1519" s="4">
+        <v>526</v>
+      </c>
+      <c r="B1519" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1519" s="8">
+        <v>125139</v>
+      </c>
+      <c r="D1519" s="11">
+        <v>46260.656516157411</v>
+      </c>
+      <c r="E1519" s="8" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1519" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1519" s="8" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H1519" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1519" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1519" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1519" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1519" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="M1519" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1520" s="4">
+        <v>527</v>
+      </c>
+      <c r="B1520" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1520" s="8">
+        <v>124378</v>
+      </c>
+      <c r="D1520" s="11">
+        <v>46260.664259895842</v>
+      </c>
+      <c r="E1520" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1520" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1520" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="H1520" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1520" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1520" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1520" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1520" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="M1520" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1521" s="4">
+        <v>528</v>
+      </c>
+      <c r="B1521" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1521" s="8">
+        <v>110980</v>
+      </c>
+      <c r="D1521" s="11">
+        <v>46260.670854861113</v>
+      </c>
+      <c r="E1521" s="8" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F1521" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1521" s="8" t="s">
+        <v>1748</v>
+      </c>
+      <c r="H1521" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1521" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1521" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1521" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1521" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="M1521" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1522" s="4">
+        <v>529</v>
+      </c>
+      <c r="B1522" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1522" s="8">
+        <v>120498</v>
+      </c>
+      <c r="D1522" s="11">
+        <v>46260.698743657413</v>
+      </c>
+      <c r="E1522" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1522" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1522" s="8" t="s">
+        <v>1749</v>
+      </c>
+      <c r="H1522" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1522" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1522" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1522" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1522" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="M1522" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1523" s="4">
+        <v>530</v>
+      </c>
+      <c r="B1523" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1523" s="8">
+        <v>121901</v>
+      </c>
+      <c r="D1523" s="11">
+        <v>46260.70864798611</v>
+      </c>
+      <c r="E1523" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1523" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1523" s="8" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H1523" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1523" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1523" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1523" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1523" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M1523" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1524" s="4">
+        <v>531</v>
+      </c>
+      <c r="B1524" s="8" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1524" s="8">
+        <v>126105</v>
+      </c>
+      <c r="D1524" s="11">
+        <v>46260.825613090281</v>
+      </c>
+      <c r="E1524" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="F1524" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1524" s="8" t="s">
+        <v>1751</v>
+      </c>
+      <c r="H1524" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1524" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1524" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1524" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1524" s="4" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M1524" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1525" s="4">
+        <v>532</v>
+      </c>
+      <c r="B1525" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1525" s="8">
+        <v>21536</v>
+      </c>
+      <c r="D1525" s="11">
+        <v>46260.895230983799</v>
+      </c>
+      <c r="E1525" s="8" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1525" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1525" s="8" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H1525" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1525" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1525" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K1525" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1525" s="4" t="s">
+        <v>1764</v>
+      </c>
+      <c r="M1525" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1092" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FBCB330-930F-4737-9BDD-71485F7A6B04}"/>
+  <xr:revisionPtr revIDLastSave="1113" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3901553-C985-4D5A-B2FD-302E43027E44}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12536" uniqueCount="1799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12572" uniqueCount="1805">
   <si>
     <t>ID</t>
   </si>
@@ -5660,6 +5660,24 @@
   </si>
   <si>
     <t>mensagens do WhatsApp não são cumpridas</t>
+  </si>
+  <si>
+    <t>02/09/2026</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
+    <t>Ele veio para fazer a manutencao preventiva dentre ela a troca do filtro e depois de 6 meses disse que nao era necessario. Foi embora sem higienizar o aparelho ou trocar o filtro. Para que manutencao de 6 em 6 meses se nem o filtro foi trocado?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A pior possível, sou cliente há 14 anos e nunca me senti tão mal atendido, solicitei uma visita, pois meu filtro está fazendo um barulho insuportável, o técnico confirmou o problema, ao enviar um vídeo para central a atendente disse que não havia problema algum no filtro na minha cara e do técnico, reintero que o técnico foi ótimo, sabia o que estava fazendo e falando, mas uma funcionária de dentro de um escritório no ar condicionado fala na minha cara que meu filtro não tem problema nenhum. Vou cancelar! </t>
+  </si>
+  <si>
+    <t>O meu aparelho foi instalado a menos de uma semana e já apresentou defeito, manutenção só acontecerá após 2 dias.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meu filtro não tem nem dois meses e já deu problema. Queria que mudassem para um novo </t>
   </si>
 </sst>
 </file>
@@ -5751,7 +5769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5785,6 +5803,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6127,7 +6148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1543"/>
+  <dimension ref="A1:M1547"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -60568,6 +60589,134 @@
         <v>1685</v>
       </c>
     </row>
+    <row r="1544" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1544" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C1544" s="4">
+        <v>116728</v>
+      </c>
+      <c r="D1544" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E1544" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F1544" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1544" s="4" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H1544" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1544" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1544" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K1544" s="4" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1545" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1545" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C1545" s="4">
+        <v>134157</v>
+      </c>
+      <c r="D1545" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E1545" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F1545" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1545" s="4" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1545" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1545" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1545" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K1545" s="4" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1546" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1546" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1546" s="4">
+        <v>132917</v>
+      </c>
+      <c r="D1546" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E1546" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="F1546" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1546" s="4" t="s">
+        <v>1803</v>
+      </c>
+      <c r="H1546" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1546" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1546" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K1546" s="4" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1547" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1547" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C1547" s="4">
+        <v>131662</v>
+      </c>
+      <c r="D1547" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E1547" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1547" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1547" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H1547" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1547" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1547" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K1547" s="4" t="s">
+        <v>1434</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3901553-C985-4D5A-B2FD-302E43027E44}"/>
+  <xr:revisionPtr revIDLastSave="1134" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A18CB5A-E8A8-4F7E-B776-32BA5B3BAB2C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1547</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5769,7 +5769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5806,6 +5806,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -55730,7 +55733,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="1417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1417" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A1417" s="4">
         <v>421</v>
       </c>
@@ -55749,7 +55752,7 @@
       <c r="F1417" s="4" t="s">
         <v>1458</v>
       </c>
-      <c r="G1417" s="4" t="s">
+      <c r="G1417" s="5" t="s">
         <v>1585</v>
       </c>
       <c r="H1417" s="4" t="s">
@@ -56535,7 +56538,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="1440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1440" spans="1:11" ht="210" x14ac:dyDescent="0.25">
       <c r="A1440" s="4">
         <v>444</v>
       </c>
@@ -56554,7 +56557,7 @@
       <c r="F1440" t="s">
         <v>16</v>
       </c>
-      <c r="G1440" s="8" t="s">
+      <c r="G1440" s="13" t="s">
         <v>1609</v>
       </c>
       <c r="H1440" s="4" t="s">
@@ -56605,7 +56608,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="1442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1442" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A1442" s="4">
         <v>447</v>
       </c>
@@ -56624,7 +56627,7 @@
       <c r="F1442" t="s">
         <v>16</v>
       </c>
-      <c r="G1442" s="8" t="s">
+      <c r="G1442" s="13" t="s">
         <v>1611</v>
       </c>
       <c r="H1442" s="4" t="s">
@@ -57568,7 +57571,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="1469" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1469" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A1469" s="4">
         <v>476</v>
       </c>
@@ -57587,14 +57590,14 @@
       <c r="F1469" t="s">
         <v>16</v>
       </c>
-      <c r="G1469" s="8" t="s">
+      <c r="G1469" s="13" t="s">
         <v>1640</v>
       </c>
       <c r="H1469" s="4" t="s">
-        <v>80</v>
+        <v>1528</v>
       </c>
       <c r="I1469" s="4" t="s">
-        <v>81</v>
+        <v>1555</v>
       </c>
       <c r="J1469" s="4" t="s">
         <v>1399</v>
@@ -57960,10 +57963,10 @@
         <v>1631</v>
       </c>
       <c r="H1478" s="4" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="I1478" s="4" t="s">
-        <v>414</v>
+        <v>26</v>
       </c>
       <c r="J1478" s="4" t="s">
         <v>1399</v>
@@ -58329,10 +58332,10 @@
         <v>1658</v>
       </c>
       <c r="H1487" s="4" t="s">
-        <v>80</v>
+        <v>1528</v>
       </c>
       <c r="I1487" s="4" t="s">
-        <v>81</v>
+        <v>1555</v>
       </c>
       <c r="J1487" s="4" t="s">
         <v>1399</v>
